--- a/producer/baltra.xlsx
+++ b/producer/baltra.xlsx
@@ -16,13 +16,13 @@
     <t>Product Name</t>
   </si>
   <si>
-    <t>Price (Rs.)</t>
+    <t>Price</t>
   </si>
   <si>
     <t>Description</t>
   </si>
   <si>
-    <t>Image URL</t>
+    <t>Product Image</t>
   </si>
   <si>
     <t>BALTRA Stand Fan Super Fast+ 16 inch osciliation Fan 3 speed control Low noise operation With remote 24 months warranty</t>
@@ -1339,10 +1339,10 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+      <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
@@ -1577,13 +1577,13 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
       <c r="B2" s="1">
         <v>4025.0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="1" t="s">
@@ -1608,7 +1608,7 @@
       <c r="B3" s="1">
         <v>4375.0</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1622,7 +1622,7 @@
       <c r="B4" s="1">
         <v>1925.0</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D4" s="1" t="s">
@@ -1636,7 +1636,7 @@
       <c r="B5" s="1">
         <v>3775.0</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -1650,7 +1650,7 @@
       <c r="B6" s="1">
         <v>3475.0</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -1664,7 +1664,7 @@
       <c r="B7" s="1">
         <v>3525.0</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D7" s="1" t="s">
@@ -1678,7 +1678,7 @@
       <c r="B8" s="1">
         <v>7250.0</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D8" s="1" t="s">
@@ -1692,7 +1692,7 @@
       <c r="B9" s="1">
         <v>2775.0</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>18</v>
       </c>
       <c r="D9" s="1" t="s">
@@ -1706,7 +1706,7 @@
       <c r="B10" s="1">
         <v>9575.0</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -1720,7 +1720,7 @@
       <c r="B11" s="1">
         <v>4725.0</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D11" s="1" t="s">
@@ -1734,7 +1734,7 @@
       <c r="B12" s="1">
         <v>1925.0</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D12" s="1" t="s">
@@ -1748,7 +1748,7 @@
       <c r="B13" s="1">
         <v>1925.0</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D13" s="1" t="s">
@@ -1762,7 +1762,7 @@
       <c r="B14" s="1">
         <v>1475.0</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D14" s="1" t="s">
@@ -1776,7 +1776,7 @@
       <c r="B15" s="1">
         <v>3775.0</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D15" s="1" t="s">
@@ -1790,7 +1790,7 @@
       <c r="B16" s="1">
         <v>3675.0</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="D16" s="1" t="s">
@@ -1804,7 +1804,7 @@
       <c r="B17" s="1">
         <v>3475.0</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D17" s="1" t="s">
@@ -1818,7 +1818,7 @@
       <c r="B18" s="1">
         <v>3575.0</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D18" s="1" t="s">
@@ -1832,7 +1832,7 @@
       <c r="B19" s="1">
         <v>3075.0</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="3" t="s">
         <v>38</v>
       </c>
       <c r="D19" s="1" t="s">
@@ -1846,7 +1846,7 @@
       <c r="B20" s="1">
         <v>8825.0</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="3" t="s">
         <v>40</v>
       </c>
       <c r="D20" s="1" t="s">
@@ -1860,7 +1860,7 @@
       <c r="B21" s="1">
         <v>1925.0</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="3" t="s">
         <v>42</v>
       </c>
       <c r="D21" s="1" t="s">
@@ -1874,7 +1874,7 @@
       <c r="B22" s="1">
         <v>3475.0</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D22" s="1" t="s">
@@ -1888,7 +1888,7 @@
       <c r="B23" s="1">
         <v>7525.0</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="3" t="s">
         <v>46</v>
       </c>
       <c r="D23" s="1" t="s">
@@ -1902,7 +1902,7 @@
       <c r="B24" s="1">
         <v>3575.0</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="3" t="s">
         <v>48</v>
       </c>
       <c r="D24" s="1" t="s">
@@ -1916,7 +1916,7 @@
       <c r="B25" s="1">
         <v>4675.0</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="3" t="s">
         <v>50</v>
       </c>
       <c r="D25" s="1" t="s">
@@ -1930,7 +1930,7 @@
       <c r="B26" s="1">
         <v>8825.0</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="3" t="s">
         <v>52</v>
       </c>
       <c r="D26" s="1" t="s">
@@ -1944,7 +1944,7 @@
       <c r="B27" s="1">
         <v>2575.0</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="3" t="s">
         <v>55</v>
       </c>
       <c r="D27" s="1" t="s">
@@ -1958,7 +1958,7 @@
       <c r="B28" s="1">
         <v>1450.0</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="3" t="s">
         <v>57</v>
       </c>
       <c r="D28" s="1" t="s">
@@ -1972,7 +1972,7 @@
       <c r="B29" s="1">
         <v>1575.0</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="3" t="s">
         <v>59</v>
       </c>
       <c r="D29" s="1" t="s">
@@ -1986,7 +1986,7 @@
       <c r="B30" s="1">
         <v>1650.0</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="3" t="s">
         <v>61</v>
       </c>
       <c r="D30" s="1" t="s">
@@ -2000,7 +2000,7 @@
       <c r="B31" s="1">
         <v>1150.0</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="3" t="s">
         <v>63</v>
       </c>
       <c r="D31" s="1" t="s">
@@ -2014,7 +2014,7 @@
       <c r="B32" s="1">
         <v>2475.0</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="3" t="s">
         <v>65</v>
       </c>
       <c r="D32" s="1" t="s">
@@ -2028,7 +2028,7 @@
       <c r="B33" s="1">
         <v>2275.0</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="3" t="s">
         <v>67</v>
       </c>
       <c r="D33" s="1" t="s">
@@ -2042,7 +2042,7 @@
       <c r="B34" s="1">
         <v>2475.0</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="3" t="s">
         <v>69</v>
       </c>
       <c r="D34" s="1" t="s">
@@ -2056,7 +2056,7 @@
       <c r="B35" s="1">
         <v>2650.0</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="3" t="s">
         <v>71</v>
       </c>
       <c r="D35" s="1" t="s">
@@ -2067,7 +2067,7 @@
       <c r="A36" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B36" s="3">
+      <c r="B36" s="2">
         <v>3275.0</v>
       </c>
       <c r="C36" s="4" t="s">
@@ -2084,7 +2084,7 @@
       <c r="B37" s="1">
         <v>1525.0</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="3" t="s">
         <v>73</v>
       </c>
       <c r="D37" s="1" t="s">
@@ -2098,7 +2098,7 @@
       <c r="B38" s="1">
         <v>1575.0</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="3" t="s">
         <v>76</v>
       </c>
       <c r="D38" s="1" t="s">
@@ -2112,7 +2112,7 @@
       <c r="B39" s="1">
         <v>2925.0</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="3" t="s">
         <v>78</v>
       </c>
       <c r="D39" s="1" t="s">
@@ -2126,7 +2126,7 @@
       <c r="B40" s="1">
         <v>1575.0</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="3" t="s">
         <v>79</v>
       </c>
       <c r="D40" s="1" t="s">
@@ -2140,7 +2140,7 @@
       <c r="B41" s="1">
         <v>1575.0</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="3" t="s">
         <v>81</v>
       </c>
       <c r="D41" s="1" t="s">
@@ -2154,7 +2154,7 @@
       <c r="B42" s="1">
         <v>1575.0</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="3" t="s">
         <v>83</v>
       </c>
       <c r="D42" s="1" t="s">
@@ -2168,7 +2168,7 @@
       <c r="B43" s="1">
         <v>1675.0</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="3" t="s">
         <v>85</v>
       </c>
       <c r="D43" s="1" t="s">
@@ -2182,7 +2182,7 @@
       <c r="B44" s="1">
         <v>2075.0</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="3" t="s">
         <v>87</v>
       </c>
       <c r="D44" s="1" t="s">
@@ -2196,7 +2196,7 @@
       <c r="B45" s="1">
         <v>1150.0</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="3" t="s">
         <v>89</v>
       </c>
       <c r="D45" s="1" t="s">
@@ -2210,7 +2210,7 @@
       <c r="B46" s="1">
         <v>1150.0</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="3" t="s">
         <v>91</v>
       </c>
       <c r="D46" s="1" t="s">
@@ -2224,7 +2224,7 @@
       <c r="B47" s="1">
         <v>1675.0</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="3" t="s">
         <v>93</v>
       </c>
       <c r="D47" s="1" t="s">
@@ -2238,7 +2238,7 @@
       <c r="B48" s="1">
         <v>1675.0</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="3" t="s">
         <v>96</v>
       </c>
       <c r="D48" s="1" t="s">
@@ -2252,7 +2252,7 @@
       <c r="B49" s="1">
         <v>3075.0</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="3" t="s">
         <v>99</v>
       </c>
       <c r="D49" s="1" t="s">
@@ -2266,7 +2266,7 @@
       <c r="B50" s="1">
         <v>1125.0</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="3" t="s">
         <v>101</v>
       </c>
       <c r="D50" s="1" t="s">
@@ -2277,7 +2277,7 @@
       <c r="A51" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B51" s="3">
+      <c r="B51" s="2">
         <v>4575.0</v>
       </c>
       <c r="C51" s="4" t="s">
@@ -2294,7 +2294,7 @@
       <c r="B52" s="1">
         <v>3975.0</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="3" t="s">
         <v>106</v>
       </c>
       <c r="D52" s="1" t="s">
@@ -2305,7 +2305,7 @@
       <c r="A53" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B53" s="3">
+      <c r="B53" s="2">
         <v>4175.0</v>
       </c>
       <c r="C53" s="4" t="s">
@@ -2322,7 +2322,7 @@
       <c r="B54" s="1">
         <v>9975.0</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="3" t="s">
         <v>111</v>
       </c>
       <c r="D54" s="1" t="s">
@@ -2336,7 +2336,7 @@
       <c r="B55" s="1">
         <v>6125.0</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="3" t="s">
         <v>114</v>
       </c>
       <c r="D55" s="1" t="s">
@@ -2350,7 +2350,7 @@
       <c r="B56" s="1">
         <v>7075.0</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" s="3" t="s">
         <v>117</v>
       </c>
       <c r="D56" s="1" t="s">
@@ -2364,7 +2364,7 @@
       <c r="B57" s="1">
         <v>4425.0</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" s="3" t="s">
         <v>120</v>
       </c>
       <c r="D57" s="1" t="s">
@@ -2375,7 +2375,7 @@
       <c r="A58" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B58" s="3">
+      <c r="B58" s="2">
         <v>5775.0</v>
       </c>
       <c r="C58" s="4" t="s">
@@ -2392,7 +2392,7 @@
       <c r="B59" s="1">
         <v>4350.0</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="3" t="s">
         <v>125</v>
       </c>
       <c r="D59" s="1" t="s">
@@ -2406,7 +2406,7 @@
       <c r="B60" s="1">
         <v>4375.0</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="3" t="s">
         <v>128</v>
       </c>
       <c r="D60" s="1" t="s">
@@ -2420,7 +2420,7 @@
       <c r="B61" s="1">
         <v>16575.0</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" s="3" t="s">
         <v>131</v>
       </c>
       <c r="D61" s="1" t="s">
@@ -2434,7 +2434,7 @@
       <c r="B62" s="1">
         <v>6975.0</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C62" s="3" t="s">
         <v>134</v>
       </c>
       <c r="D62" s="1" t="s">
@@ -2445,7 +2445,7 @@
       <c r="A63" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B63" s="3">
+      <c r="B63" s="2">
         <v>11275.0</v>
       </c>
       <c r="C63" s="4" t="s">
@@ -2462,7 +2462,7 @@
       <c r="B64" s="1">
         <v>3925.0</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C64" s="3" t="s">
         <v>139</v>
       </c>
       <c r="D64" s="1" t="s">
@@ -2476,7 +2476,7 @@
       <c r="B65" s="1">
         <v>3975.0</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C65" s="3" t="s">
         <v>106</v>
       </c>
       <c r="D65" s="1" t="s">
@@ -2490,7 +2490,7 @@
       <c r="B66" s="1">
         <v>3975.0</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C66" s="3" t="s">
         <v>144</v>
       </c>
       <c r="D66" s="1" t="s">
@@ -2515,7 +2515,7 @@
       <c r="A68" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B68" s="3">
+      <c r="B68" s="2">
         <v>4325.0</v>
       </c>
       <c r="C68" s="4" t="s">
@@ -2532,7 +2532,7 @@
       <c r="B69" s="1">
         <v>4075.0</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="3" t="s">
         <v>151</v>
       </c>
       <c r="D69" s="1" t="s">
@@ -2546,7 +2546,7 @@
       <c r="B70" s="1">
         <v>3925.0</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" s="3" t="s">
         <v>154</v>
       </c>
       <c r="D70" s="1" t="s">
@@ -2560,7 +2560,7 @@
       <c r="B71" s="1">
         <v>3125.0</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C71" s="3" t="s">
         <v>157</v>
       </c>
       <c r="D71" s="1" t="s">
@@ -2574,7 +2574,7 @@
       <c r="B72" s="1">
         <v>4575.0</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C72" s="3" t="s">
         <v>160</v>
       </c>
       <c r="D72" s="1" t="s">
@@ -2588,7 +2588,7 @@
       <c r="B73" s="1">
         <v>29575.0</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="C73" s="3" t="s">
         <v>163</v>
       </c>
       <c r="D73" s="1" t="s">
@@ -2602,7 +2602,7 @@
       <c r="B74" s="1">
         <v>8075.0</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C74" s="3" t="s">
         <v>166</v>
       </c>
       <c r="D74" s="1" t="s">
@@ -2616,7 +2616,7 @@
       <c r="B75" s="1">
         <v>13025.0</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="C75" s="3" t="s">
         <v>169</v>
       </c>
       <c r="D75" s="1" t="s">
@@ -2630,7 +2630,7 @@
       <c r="B76" s="1">
         <v>4025.0</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="C76" s="3" t="s">
         <v>172</v>
       </c>
       <c r="D76" s="1" t="s">
@@ -2644,7 +2644,7 @@
       <c r="B77" s="1">
         <v>9975.0</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="C77" s="3" t="s">
         <v>175</v>
       </c>
       <c r="D77" s="1" t="s">
@@ -2658,7 +2658,7 @@
       <c r="B78" s="1">
         <v>4575.0</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C78" s="3" t="s">
         <v>178</v>
       </c>
       <c r="D78" s="1" t="s">
@@ -2672,7 +2672,7 @@
       <c r="B79" s="1">
         <v>15575.0</v>
       </c>
-      <c r="C79" s="2" t="s">
+      <c r="C79" s="3" t="s">
         <v>181</v>
       </c>
       <c r="D79" s="1" t="s">
@@ -2686,7 +2686,7 @@
       <c r="B80" s="1">
         <v>4125.0</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="C80" s="3" t="s">
         <v>184</v>
       </c>
       <c r="D80" s="1" t="s">
@@ -2700,7 +2700,7 @@
       <c r="B81" s="1">
         <v>8075.0</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="C81" s="3" t="s">
         <v>187</v>
       </c>
       <c r="D81" s="1" t="s">
@@ -2714,7 +2714,7 @@
       <c r="B82" s="1">
         <v>11725.0</v>
       </c>
-      <c r="C82" s="2" t="s">
+      <c r="C82" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D82" s="1" t="s">
@@ -2728,7 +2728,7 @@
       <c r="B83" s="1">
         <v>14125.0</v>
       </c>
-      <c r="C83" s="2" t="s">
+      <c r="C83" s="3" t="s">
         <v>193</v>
       </c>
       <c r="D83" s="1" t="s">
@@ -2742,7 +2742,7 @@
       <c r="B84" s="1">
         <v>4025.0</v>
       </c>
-      <c r="C84" s="2" t="s">
+      <c r="C84" s="3" t="s">
         <v>196</v>
       </c>
       <c r="D84" s="1" t="s">
@@ -2756,7 +2756,7 @@
       <c r="B85" s="1">
         <v>9975.0</v>
       </c>
-      <c r="C85" s="2" t="s">
+      <c r="C85" s="3" t="s">
         <v>199</v>
       </c>
       <c r="D85" s="1" t="s">
@@ -2767,7 +2767,7 @@
       <c r="A86" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B86" s="3">
+      <c r="B86" s="2">
         <v>17525.0</v>
       </c>
       <c r="C86" s="4" t="s">
@@ -2784,7 +2784,7 @@
       <c r="B87" s="1">
         <v>4125.0</v>
       </c>
-      <c r="C87" s="2" t="s">
+      <c r="C87" s="3" t="s">
         <v>204</v>
       </c>
       <c r="D87" s="1" t="s">
@@ -2798,7 +2798,7 @@
       <c r="B88" s="1">
         <v>17525.0</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="C88" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D88" s="1" t="s">
@@ -2812,7 +2812,7 @@
       <c r="B89" s="1">
         <v>4275.0</v>
       </c>
-      <c r="C89" s="2" t="s">
+      <c r="C89" s="3" t="s">
         <v>210</v>
       </c>
       <c r="D89" s="1" t="s">
@@ -2826,7 +2826,7 @@
       <c r="B90" s="1">
         <v>15075.0</v>
       </c>
-      <c r="C90" s="2" t="s">
+      <c r="C90" s="3" t="s">
         <v>213</v>
       </c>
       <c r="D90" s="1" t="s">
@@ -2840,7 +2840,7 @@
       <c r="B91" s="1">
         <v>29975.0</v>
       </c>
-      <c r="C91" s="2" t="s">
+      <c r="C91" s="3" t="s">
         <v>216</v>
       </c>
       <c r="D91" s="1" t="s">
@@ -2854,7 +2854,7 @@
       <c r="B92" s="1">
         <v>16075.0</v>
       </c>
-      <c r="C92" s="2" t="s">
+      <c r="C92" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D92" s="1" t="s">
@@ -2868,7 +2868,7 @@
       <c r="B93" s="1">
         <v>23975.0</v>
       </c>
-      <c r="C93" s="2" t="s">
+      <c r="C93" s="3" t="s">
         <v>222</v>
       </c>
       <c r="D93" s="1" t="s">
@@ -2882,7 +2882,7 @@
       <c r="B94" s="1">
         <v>17075.0</v>
       </c>
-      <c r="C94" s="2" t="s">
+      <c r="C94" s="3" t="s">
         <v>225</v>
       </c>
       <c r="D94" s="1" t="s">
@@ -2896,7 +2896,7 @@
       <c r="B95" s="1">
         <v>15075.0</v>
       </c>
-      <c r="C95" s="2" t="s">
+      <c r="C95" s="3" t="s">
         <v>228</v>
       </c>
       <c r="D95" s="1" t="s">
@@ -2910,7 +2910,7 @@
       <c r="B96" s="1">
         <v>17575.0</v>
       </c>
-      <c r="C96" s="2" t="s">
+      <c r="C96" s="3" t="s">
         <v>230</v>
       </c>
       <c r="D96" s="1" t="s">
@@ -2924,7 +2924,7 @@
       <c r="B97" s="1">
         <v>15075.0</v>
       </c>
-      <c r="C97" s="2" t="s">
+      <c r="C97" s="3" t="s">
         <v>233</v>
       </c>
       <c r="D97" s="1" t="s">
@@ -2938,7 +2938,7 @@
       <c r="B98" s="1">
         <v>22775.0</v>
       </c>
-      <c r="C98" s="2" t="s">
+      <c r="C98" s="3" t="s">
         <v>235</v>
       </c>
       <c r="D98" s="1" t="s">
@@ -2952,7 +2952,7 @@
       <c r="B99" s="1">
         <v>27575.0</v>
       </c>
-      <c r="C99" s="2" t="s">
+      <c r="C99" s="3" t="s">
         <v>238</v>
       </c>
       <c r="D99" s="1" t="s">
@@ -2966,7 +2966,7 @@
       <c r="B100" s="1">
         <v>15575.0</v>
       </c>
-      <c r="C100" s="2" t="s">
+      <c r="C100" s="3" t="s">
         <v>240</v>
       </c>
       <c r="D100" s="1" t="s">
@@ -2980,7 +2980,7 @@
       <c r="B101" s="1">
         <v>19575.0</v>
       </c>
-      <c r="C101" s="2" t="s">
+      <c r="C101" s="3" t="s">
         <v>242</v>
       </c>
       <c r="D101" s="1" t="s">
@@ -2994,7 +2994,7 @@
       <c r="B102" s="1">
         <v>21275.0</v>
       </c>
-      <c r="C102" s="2" t="s">
+      <c r="C102" s="3" t="s">
         <v>245</v>
       </c>
       <c r="D102" s="1" t="s">
@@ -3008,7 +3008,7 @@
       <c r="B103" s="1">
         <v>13475.0</v>
       </c>
-      <c r="C103" s="2" t="s">
+      <c r="C103" s="3" t="s">
         <v>247</v>
       </c>
       <c r="D103" s="1" t="s">
@@ -3022,7 +3022,7 @@
       <c r="B104" s="1">
         <v>1225.0</v>
       </c>
-      <c r="C104" s="2" t="s">
+      <c r="C104" s="3" t="s">
         <v>250</v>
       </c>
       <c r="D104" s="1" t="s">
@@ -3036,7 +3036,7 @@
       <c r="B105" s="1">
         <v>10975.0</v>
       </c>
-      <c r="C105" s="2" t="s">
+      <c r="C105" s="3" t="s">
         <v>253</v>
       </c>
       <c r="D105" s="1" t="s">
@@ -3050,7 +3050,7 @@
       <c r="B106" s="1">
         <v>1375.0</v>
       </c>
-      <c r="C106" s="2" t="s">
+      <c r="C106" s="3" t="s">
         <v>256</v>
       </c>
       <c r="D106" s="1" t="s">
@@ -3061,7 +3061,7 @@
       <c r="A107" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B107" s="3">
+      <c r="B107" s="2">
         <v>3125.0</v>
       </c>
       <c r="C107" s="4" t="s">
@@ -3078,7 +3078,7 @@
       <c r="B108" s="1">
         <v>13975.0</v>
       </c>
-      <c r="C108" s="2" t="s">
+      <c r="C108" s="3" t="s">
         <v>261</v>
       </c>
       <c r="D108" s="1" t="s">
@@ -3092,7 +3092,7 @@
       <c r="B109" s="1">
         <v>1175.0</v>
       </c>
-      <c r="C109" s="2" t="s">
+      <c r="C109" s="3" t="s">
         <v>264</v>
       </c>
       <c r="D109" s="1" t="s">
@@ -3106,7 +3106,7 @@
       <c r="B110" s="1">
         <v>2875.0</v>
       </c>
-      <c r="C110" s="2" t="s">
+      <c r="C110" s="3" t="s">
         <v>267</v>
       </c>
       <c r="D110" s="1" t="s">
@@ -3120,7 +3120,7 @@
       <c r="B111" s="1">
         <v>2375.0</v>
       </c>
-      <c r="C111" s="2" t="s">
+      <c r="C111" s="3" t="s">
         <v>270</v>
       </c>
       <c r="D111" s="1" t="s">
@@ -3134,7 +3134,7 @@
       <c r="B112" s="1">
         <v>8525.0</v>
       </c>
-      <c r="C112" s="2" t="s">
+      <c r="C112" s="3" t="s">
         <v>273</v>
       </c>
       <c r="D112" s="1" t="s">
@@ -3148,7 +3148,7 @@
       <c r="B113" s="1">
         <v>3275.0</v>
       </c>
-      <c r="C113" s="2" t="s">
+      <c r="C113" s="3" t="s">
         <v>276</v>
       </c>
       <c r="D113" s="1" t="s">
@@ -3162,7 +3162,7 @@
       <c r="B114" s="1">
         <v>16975.0</v>
       </c>
-      <c r="C114" s="2" t="s">
+      <c r="C114" s="3" t="s">
         <v>279</v>
       </c>
       <c r="D114" s="1" t="s">
@@ -3176,7 +3176,7 @@
       <c r="B115" s="1">
         <v>18975.0</v>
       </c>
-      <c r="C115" s="2" t="s">
+      <c r="C115" s="3" t="s">
         <v>282</v>
       </c>
       <c r="D115" s="1" t="s">
@@ -3190,7 +3190,7 @@
       <c r="B116" s="1">
         <v>1250.0</v>
       </c>
-      <c r="C116" s="2" t="s">
+      <c r="C116" s="3" t="s">
         <v>284</v>
       </c>
       <c r="D116" s="1" t="s">
@@ -3204,7 +3204,7 @@
       <c r="B117" s="1">
         <v>1050.0</v>
       </c>
-      <c r="C117" s="2" t="s">
+      <c r="C117" s="3" t="s">
         <v>287</v>
       </c>
       <c r="D117" s="1" t="s">
@@ -3218,7 +3218,7 @@
       <c r="B118" s="1">
         <v>20375.0</v>
       </c>
-      <c r="C118" s="2" t="s">
+      <c r="C118" s="3" t="s">
         <v>289</v>
       </c>
       <c r="D118" s="1" t="s">
@@ -3232,7 +3232,7 @@
       <c r="B119" s="1">
         <v>23475.0</v>
       </c>
-      <c r="C119" s="2" t="s">
+      <c r="C119" s="3" t="s">
         <v>292</v>
       </c>
       <c r="D119" s="1" t="s">
@@ -3246,7 +3246,7 @@
       <c r="B120" s="1">
         <v>1150.0</v>
       </c>
-      <c r="C120" s="2" t="s">
+      <c r="C120" s="3" t="s">
         <v>294</v>
       </c>
       <c r="D120" s="1" t="s">
@@ -3260,7 +3260,7 @@
       <c r="B121" s="1">
         <v>24575.0</v>
       </c>
-      <c r="C121" s="2" t="s">
+      <c r="C121" s="3" t="s">
         <v>296</v>
       </c>
       <c r="D121" s="1" t="s">
@@ -3274,7 +3274,7 @@
       <c r="B122" s="1">
         <v>11775.0</v>
       </c>
-      <c r="C122" s="2" t="s">
+      <c r="C122" s="3" t="s">
         <v>299</v>
       </c>
       <c r="D122" s="1" t="s">
@@ -3288,7 +3288,7 @@
       <c r="B123" s="1">
         <v>15575.0</v>
       </c>
-      <c r="C123" s="2" t="s">
+      <c r="C123" s="3" t="s">
         <v>302</v>
       </c>
       <c r="D123" s="1" t="s">
@@ -3302,7 +3302,7 @@
       <c r="B124" s="1">
         <v>8775.0</v>
       </c>
-      <c r="C124" s="2" t="s">
+      <c r="C124" s="3" t="s">
         <v>305</v>
       </c>
       <c r="D124" s="1" t="s">
@@ -3316,7 +3316,7 @@
       <c r="B125" s="1">
         <v>23475.0</v>
       </c>
-      <c r="C125" s="2" t="s">
+      <c r="C125" s="3" t="s">
         <v>308</v>
       </c>
       <c r="D125" s="1" t="s">
@@ -3330,7 +3330,7 @@
       <c r="B126" s="1">
         <v>20375.0</v>
       </c>
-      <c r="C126" s="2" t="s">
+      <c r="C126" s="3" t="s">
         <v>311</v>
       </c>
       <c r="D126" s="1" t="s">
@@ -3344,7 +3344,7 @@
       <c r="B127" s="1">
         <v>20575.0</v>
       </c>
-      <c r="C127" s="2" t="s">
+      <c r="C127" s="3" t="s">
         <v>313</v>
       </c>
       <c r="D127" s="1" t="s">
@@ -3358,7 +3358,7 @@
       <c r="B128" s="1">
         <v>10175.0</v>
       </c>
-      <c r="C128" s="2" t="s">
+      <c r="C128" s="3" t="s">
         <v>315</v>
       </c>
       <c r="D128" s="1" t="s">
@@ -3372,7 +3372,7 @@
       <c r="B129" s="1">
         <v>1250.0</v>
       </c>
-      <c r="C129" s="2" t="s">
+      <c r="C129" s="3" t="s">
         <v>318</v>
       </c>
       <c r="D129" s="1" t="s">
@@ -3386,7 +3386,7 @@
       <c r="B130" s="1">
         <v>1075.0</v>
       </c>
-      <c r="C130" s="2" t="s">
+      <c r="C130" s="3" t="s">
         <v>321</v>
       </c>
       <c r="D130" s="1" t="s">
@@ -3397,10 +3397,10 @@
       <c r="A131" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B131" s="3">
+      <c r="B131" s="2">
         <v>3174.0</v>
       </c>
-      <c r="C131" s="2" t="s">
+      <c r="C131" s="3" t="s">
         <v>324</v>
       </c>
       <c r="D131" s="1" t="s">
@@ -3411,10 +3411,10 @@
       <c r="A132" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B132" s="3">
+      <c r="B132" s="2">
         <v>3075.0</v>
       </c>
-      <c r="C132" s="2" t="s">
+      <c r="C132" s="3" t="s">
         <v>324</v>
       </c>
       <c r="D132" s="6" t="s">
@@ -3425,7 +3425,7 @@
       <c r="A133" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B133" s="3">
+      <c r="B133" s="2">
         <v>3125.0</v>
       </c>
       <c r="C133" s="4" t="s">
@@ -3442,10 +3442,10 @@
       <c r="A134" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B134" s="3">
+      <c r="B134" s="2">
         <v>1775.0</v>
       </c>
-      <c r="C134" s="2" t="s">
+      <c r="C134" s="3" t="s">
         <v>332</v>
       </c>
       <c r="D134" s="1" t="s">
@@ -3459,7 +3459,7 @@
       <c r="B135" s="1">
         <v>1295.0</v>
       </c>
-      <c r="C135" s="2" t="s">
+      <c r="C135" s="3" t="s">
         <v>335</v>
       </c>
       <c r="D135" s="1" t="s">
@@ -3470,7 +3470,7 @@
       <c r="A136" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="B136" s="3">
+      <c r="B136" s="2">
         <v>2225.0</v>
       </c>
       <c r="C136" s="4" t="s">
@@ -3484,7 +3484,7 @@
       <c r="A137" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="B137" s="3">
+      <c r="B137" s="2">
         <v>3175.0</v>
       </c>
       <c r="C137" s="4" t="s">
@@ -3501,7 +3501,7 @@
       <c r="B138" s="1">
         <v>2375.0</v>
       </c>
-      <c r="C138" s="2" t="s">
+      <c r="C138" s="3" t="s">
         <v>342</v>
       </c>
       <c r="D138" s="5" t="s">
@@ -3512,7 +3512,7 @@
       <c r="A139" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="B139" s="3">
+      <c r="B139" s="2">
         <v>1525.0</v>
       </c>
       <c r="C139" s="4" t="s">
@@ -3529,7 +3529,7 @@
       <c r="B140" s="1">
         <v>6875.0</v>
       </c>
-      <c r="C140" s="2" t="s">
+      <c r="C140" s="3" t="s">
         <v>347</v>
       </c>
       <c r="D140" s="1" t="s">
@@ -3543,7 +3543,7 @@
       <c r="B141" s="1">
         <v>6175.0</v>
       </c>
-      <c r="C141" s="2" t="s">
+      <c r="C141" s="3" t="s">
         <v>350</v>
       </c>
       <c r="D141" s="1" t="s">
@@ -3557,7 +3557,7 @@
       <c r="B142" s="1">
         <v>3375.0</v>
       </c>
-      <c r="C142" s="2" t="s">
+      <c r="C142" s="3" t="s">
         <v>353</v>
       </c>
       <c r="D142" s="1" t="s">
@@ -3571,7 +3571,7 @@
       <c r="B143" s="1">
         <v>17525.0</v>
       </c>
-      <c r="C143" s="2" t="s">
+      <c r="C143" s="3" t="s">
         <v>356</v>
       </c>
       <c r="D143" s="1" t="s">
@@ -3585,7 +3585,7 @@
       <c r="B144" s="1">
         <v>3225.0</v>
       </c>
-      <c r="C144" s="2" t="s">
+      <c r="C144" s="3" t="s">
         <v>359</v>
       </c>
       <c r="D144" s="1" t="s">
@@ -3599,7 +3599,7 @@
       <c r="B145" s="1">
         <v>7875.0</v>
       </c>
-      <c r="C145" s="2" t="s">
+      <c r="C145" s="3" t="s">
         <v>362</v>
       </c>
       <c r="D145" s="1" t="s">
@@ -3613,7 +3613,7 @@
       <c r="B146" s="1">
         <v>2925.0</v>
       </c>
-      <c r="C146" s="2" t="s">
+      <c r="C146" s="3" t="s">
         <v>365</v>
       </c>
       <c r="D146" s="1" t="s">
@@ -3627,7 +3627,7 @@
       <c r="B147" s="1">
         <v>3475.0</v>
       </c>
-      <c r="C147" s="2" t="s">
+      <c r="C147" s="3" t="s">
         <v>368</v>
       </c>
       <c r="D147" s="1" t="s">
@@ -3641,7 +3641,7 @@
       <c r="B148" s="1">
         <v>3575.0</v>
       </c>
-      <c r="C148" s="2" t="s">
+      <c r="C148" s="3" t="s">
         <v>371</v>
       </c>
       <c r="D148" s="1" t="s">
@@ -3655,7 +3655,7 @@
       <c r="B149" s="1">
         <v>14575.0</v>
       </c>
-      <c r="C149" s="2" t="s">
+      <c r="C149" s="3" t="s">
         <v>374</v>
       </c>
       <c r="D149" s="1" t="s">
@@ -3666,7 +3666,7 @@
       <c r="A150" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="B150" s="3">
+      <c r="B150" s="2">
         <v>8575.0</v>
       </c>
       <c r="C150" s="4" t="s">
@@ -3683,7 +3683,7 @@
       <c r="B151" s="1">
         <v>5575.0</v>
       </c>
-      <c r="C151" s="2" t="s">
+      <c r="C151" s="3" t="s">
         <v>379</v>
       </c>
       <c r="D151" s="1" t="s">
@@ -3697,7 +3697,7 @@
       <c r="B152" s="1">
         <v>23575.0</v>
       </c>
-      <c r="C152" s="2" t="s">
+      <c r="C152" s="3" t="s">
         <v>382</v>
       </c>
       <c r="D152" s="1" t="s">
@@ -3711,7 +3711,7 @@
       <c r="B153" s="1">
         <v>21575.0</v>
       </c>
-      <c r="C153" s="2" t="s">
+      <c r="C153" s="3" t="s">
         <v>385</v>
       </c>
       <c r="D153" s="1" t="s">
@@ -3725,7 +3725,7 @@
       <c r="B154" s="1">
         <v>25575.0</v>
       </c>
-      <c r="C154" s="2" t="s">
+      <c r="C154" s="3" t="s">
         <v>388</v>
       </c>
       <c r="D154" s="1" t="s">
@@ -3736,7 +3736,7 @@
       <c r="A155" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="B155" s="3">
+      <c r="B155" s="2">
         <v>13575.0</v>
       </c>
       <c r="C155" s="4" t="s">
@@ -3753,7 +3753,7 @@
       <c r="B156" s="1">
         <v>5575.0</v>
       </c>
-      <c r="C156" s="2" t="s">
+      <c r="C156" s="3" t="s">
         <v>393</v>
       </c>
       <c r="D156" s="1" t="s">
@@ -3767,7 +3767,7 @@
       <c r="B157" s="1">
         <v>5275.0</v>
       </c>
-      <c r="C157" s="2" t="s">
+      <c r="C157" s="3" t="s">
         <v>396</v>
       </c>
       <c r="D157" s="1" t="s">
@@ -3781,7 +3781,7 @@
       <c r="B158" s="1">
         <v>36775.0</v>
       </c>
-      <c r="C158" s="2" t="s">
+      <c r="C158" s="3" t="s">
         <v>399</v>
       </c>
       <c r="D158" s="1" t="s">
@@ -3795,7 +3795,7 @@
       <c r="B159" s="1">
         <v>24575.0</v>
       </c>
-      <c r="C159" s="2" t="s">
+      <c r="C159" s="3" t="s">
         <v>402</v>
       </c>
       <c r="D159" s="1" t="s">
@@ -3809,7 +3809,7 @@
       <c r="B160" s="1">
         <v>24575.0</v>
       </c>
-      <c r="C160" s="2" t="s">
+      <c r="C160" s="3" t="s">
         <v>402</v>
       </c>
       <c r="D160" s="1" t="s">
@@ -3823,7 +3823,7 @@
       <c r="B161" s="1">
         <v>1776.0</v>
       </c>
-      <c r="C161" s="2" t="s">
+      <c r="C161" s="3" t="s">
         <v>405</v>
       </c>
       <c r="D161" s="1" t="s">
@@ -3837,7 +3837,7 @@
       <c r="B162" s="1">
         <v>3175.0</v>
       </c>
-      <c r="C162" s="2" t="s">
+      <c r="C162" s="3" t="s">
         <v>408</v>
       </c>
       <c r="D162" s="1" t="s">
@@ -3848,7 +3848,7 @@
       <c r="A163" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B163" s="3">
+      <c r="B163" s="2">
         <v>1649.0</v>
       </c>
       <c r="C163" s="4" t="s">
@@ -3862,10 +3862,10 @@
       <c r="A164" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="B164" s="3">
+      <c r="B164" s="2">
         <v>3680.0</v>
       </c>
-      <c r="C164" s="2" t="s">
+      <c r="C164" s="3" t="s">
         <v>413</v>
       </c>
       <c r="D164" s="6" t="s">
@@ -3879,7 +3879,7 @@
       <c r="B165" s="1">
         <v>10575.0</v>
       </c>
-      <c r="C165" s="2" t="s">
+      <c r="C165" s="3" t="s">
         <v>416</v>
       </c>
       <c r="D165" s="1" t="s">
@@ -3893,7 +3893,7 @@
       <c r="B166" s="1">
         <v>15575.0</v>
       </c>
-      <c r="C166" s="2" t="s">
+      <c r="C166" s="3" t="s">
         <v>419</v>
       </c>
       <c r="D166" s="1" t="s">
@@ -3907,7 +3907,7 @@
       <c r="B167" s="1">
         <v>9575.0</v>
       </c>
-      <c r="C167" s="2" t="s">
+      <c r="C167" s="3" t="s">
         <v>422</v>
       </c>
       <c r="D167" s="1" t="s">
@@ -3921,7 +3921,7 @@
       <c r="B168" s="1">
         <v>9525.0</v>
       </c>
-      <c r="C168" s="2" t="s">
+      <c r="C168" s="3" t="s">
         <v>425</v>
       </c>
       <c r="D168" s="1" t="s">
@@ -3929,2470 +3929,2470 @@
       </c>
     </row>
     <row r="169" ht="15.75" customHeight="1">
-      <c r="C169" s="2"/>
+      <c r="C169" s="3"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
-      <c r="C170" s="2"/>
+      <c r="C170" s="3"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="C171" s="2"/>
+      <c r="C171" s="3"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="C172" s="2"/>
+      <c r="C172" s="3"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
-      <c r="C173" s="2"/>
+      <c r="C173" s="3"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
-      <c r="C174" s="2"/>
+      <c r="C174" s="3"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
-      <c r="C175" s="2"/>
+      <c r="C175" s="3"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
-      <c r="C176" s="2"/>
+      <c r="C176" s="3"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
-      <c r="C177" s="2"/>
+      <c r="C177" s="3"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
-      <c r="C178" s="2"/>
+      <c r="C178" s="3"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
-      <c r="C179" s="2"/>
+      <c r="C179" s="3"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
-      <c r="C180" s="2"/>
+      <c r="C180" s="3"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
-      <c r="C181" s="2"/>
+      <c r="C181" s="3"/>
     </row>
     <row r="182" ht="15.75" customHeight="1">
-      <c r="C182" s="2"/>
+      <c r="C182" s="3"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
-      <c r="C183" s="2"/>
+      <c r="C183" s="3"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
-      <c r="C184" s="2"/>
+      <c r="C184" s="3"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
-      <c r="C185" s="2"/>
+      <c r="C185" s="3"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
-      <c r="C186" s="2"/>
+      <c r="C186" s="3"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
-      <c r="C187" s="2"/>
+      <c r="C187" s="3"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
-      <c r="C188" s="2"/>
+      <c r="C188" s="3"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
-      <c r="C189" s="2"/>
+      <c r="C189" s="3"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
-      <c r="C190" s="2"/>
+      <c r="C190" s="3"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
-      <c r="C191" s="2"/>
+      <c r="C191" s="3"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
-      <c r="C192" s="2"/>
+      <c r="C192" s="3"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
-      <c r="C193" s="2"/>
+      <c r="C193" s="3"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
-      <c r="C194" s="2"/>
+      <c r="C194" s="3"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
-      <c r="C195" s="2"/>
+      <c r="C195" s="3"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
-      <c r="C196" s="2"/>
+      <c r="C196" s="3"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
-      <c r="C197" s="2"/>
+      <c r="C197" s="3"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
-      <c r="C198" s="2"/>
+      <c r="C198" s="3"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
-      <c r="C199" s="2"/>
+      <c r="C199" s="3"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
-      <c r="C200" s="2"/>
+      <c r="C200" s="3"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
-      <c r="C201" s="2"/>
+      <c r="C201" s="3"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
-      <c r="C202" s="2"/>
+      <c r="C202" s="3"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
-      <c r="C203" s="2"/>
+      <c r="C203" s="3"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
-      <c r="C204" s="2"/>
+      <c r="C204" s="3"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
-      <c r="C205" s="2"/>
+      <c r="C205" s="3"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
-      <c r="C206" s="2"/>
+      <c r="C206" s="3"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
-      <c r="C207" s="2"/>
+      <c r="C207" s="3"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
-      <c r="C208" s="2"/>
+      <c r="C208" s="3"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
-      <c r="C209" s="2"/>
+      <c r="C209" s="3"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
-      <c r="C210" s="2"/>
+      <c r="C210" s="3"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
-      <c r="C211" s="2"/>
+      <c r="C211" s="3"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
-      <c r="C212" s="2"/>
+      <c r="C212" s="3"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
-      <c r="C213" s="2"/>
+      <c r="C213" s="3"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
-      <c r="C214" s="2"/>
+      <c r="C214" s="3"/>
     </row>
     <row r="215" ht="15.75" customHeight="1">
-      <c r="C215" s="2"/>
+      <c r="C215" s="3"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
-      <c r="C216" s="2"/>
+      <c r="C216" s="3"/>
     </row>
     <row r="217" ht="15.75" customHeight="1">
-      <c r="C217" s="2"/>
+      <c r="C217" s="3"/>
     </row>
     <row r="218" ht="15.75" customHeight="1">
-      <c r="C218" s="2"/>
+      <c r="C218" s="3"/>
     </row>
     <row r="219" ht="15.75" customHeight="1">
-      <c r="C219" s="2"/>
+      <c r="C219" s="3"/>
     </row>
     <row r="220" ht="15.75" customHeight="1">
-      <c r="C220" s="2"/>
+      <c r="C220" s="3"/>
     </row>
     <row r="221" ht="15.75" customHeight="1">
-      <c r="C221" s="2"/>
+      <c r="C221" s="3"/>
     </row>
     <row r="222" ht="15.75" customHeight="1">
-      <c r="C222" s="2"/>
+      <c r="C222" s="3"/>
     </row>
     <row r="223" ht="15.75" customHeight="1">
-      <c r="C223" s="2"/>
+      <c r="C223" s="3"/>
     </row>
     <row r="224" ht="15.75" customHeight="1">
-      <c r="C224" s="2"/>
+      <c r="C224" s="3"/>
     </row>
     <row r="225" ht="15.75" customHeight="1">
-      <c r="C225" s="2"/>
+      <c r="C225" s="3"/>
     </row>
     <row r="226" ht="15.75" customHeight="1">
-      <c r="C226" s="2"/>
+      <c r="C226" s="3"/>
     </row>
     <row r="227" ht="15.75" customHeight="1">
-      <c r="C227" s="2"/>
+      <c r="C227" s="3"/>
     </row>
     <row r="228" ht="15.75" customHeight="1">
-      <c r="C228" s="2"/>
+      <c r="C228" s="3"/>
     </row>
     <row r="229" ht="15.75" customHeight="1">
-      <c r="C229" s="2"/>
+      <c r="C229" s="3"/>
     </row>
     <row r="230" ht="15.75" customHeight="1">
-      <c r="C230" s="2"/>
+      <c r="C230" s="3"/>
     </row>
     <row r="231" ht="15.75" customHeight="1">
-      <c r="C231" s="2"/>
+      <c r="C231" s="3"/>
     </row>
     <row r="232" ht="15.75" customHeight="1">
-      <c r="C232" s="2"/>
+      <c r="C232" s="3"/>
     </row>
     <row r="233" ht="15.75" customHeight="1">
-      <c r="C233" s="2"/>
+      <c r="C233" s="3"/>
     </row>
     <row r="234" ht="15.75" customHeight="1">
-      <c r="C234" s="2"/>
+      <c r="C234" s="3"/>
     </row>
     <row r="235" ht="15.75" customHeight="1">
-      <c r="C235" s="2"/>
+      <c r="C235" s="3"/>
     </row>
     <row r="236" ht="15.75" customHeight="1">
-      <c r="C236" s="2"/>
+      <c r="C236" s="3"/>
     </row>
     <row r="237" ht="15.75" customHeight="1">
-      <c r="C237" s="2"/>
+      <c r="C237" s="3"/>
     </row>
     <row r="238" ht="15.75" customHeight="1">
-      <c r="C238" s="2"/>
+      <c r="C238" s="3"/>
     </row>
     <row r="239" ht="15.75" customHeight="1">
-      <c r="C239" s="2"/>
+      <c r="C239" s="3"/>
     </row>
     <row r="240" ht="15.75" customHeight="1">
-      <c r="C240" s="2"/>
+      <c r="C240" s="3"/>
     </row>
     <row r="241" ht="15.75" customHeight="1">
-      <c r="C241" s="2"/>
+      <c r="C241" s="3"/>
     </row>
     <row r="242" ht="15.75" customHeight="1">
-      <c r="C242" s="2"/>
+      <c r="C242" s="3"/>
     </row>
     <row r="243" ht="15.75" customHeight="1">
-      <c r="C243" s="2"/>
+      <c r="C243" s="3"/>
     </row>
     <row r="244" ht="15.75" customHeight="1">
-      <c r="C244" s="2"/>
+      <c r="C244" s="3"/>
     </row>
     <row r="245" ht="15.75" customHeight="1">
-      <c r="C245" s="2"/>
+      <c r="C245" s="3"/>
     </row>
     <row r="246" ht="15.75" customHeight="1">
-      <c r="C246" s="2"/>
+      <c r="C246" s="3"/>
     </row>
     <row r="247" ht="15.75" customHeight="1">
-      <c r="C247" s="2"/>
+      <c r="C247" s="3"/>
     </row>
     <row r="248" ht="15.75" customHeight="1">
-      <c r="C248" s="2"/>
+      <c r="C248" s="3"/>
     </row>
     <row r="249" ht="15.75" customHeight="1">
-      <c r="C249" s="2"/>
+      <c r="C249" s="3"/>
     </row>
     <row r="250" ht="15.75" customHeight="1">
-      <c r="C250" s="2"/>
+      <c r="C250" s="3"/>
     </row>
     <row r="251" ht="15.75" customHeight="1">
-      <c r="C251" s="2"/>
+      <c r="C251" s="3"/>
     </row>
     <row r="252" ht="15.75" customHeight="1">
-      <c r="C252" s="2"/>
+      <c r="C252" s="3"/>
     </row>
     <row r="253" ht="15.75" customHeight="1">
-      <c r="C253" s="2"/>
+      <c r="C253" s="3"/>
     </row>
     <row r="254" ht="15.75" customHeight="1">
-      <c r="C254" s="2"/>
+      <c r="C254" s="3"/>
     </row>
     <row r="255" ht="15.75" customHeight="1">
-      <c r="C255" s="2"/>
+      <c r="C255" s="3"/>
     </row>
     <row r="256" ht="15.75" customHeight="1">
-      <c r="C256" s="2"/>
+      <c r="C256" s="3"/>
     </row>
     <row r="257" ht="15.75" customHeight="1">
-      <c r="C257" s="2"/>
+      <c r="C257" s="3"/>
     </row>
     <row r="258" ht="15.75" customHeight="1">
-      <c r="C258" s="2"/>
+      <c r="C258" s="3"/>
     </row>
     <row r="259" ht="15.75" customHeight="1">
-      <c r="C259" s="2"/>
+      <c r="C259" s="3"/>
     </row>
     <row r="260" ht="15.75" customHeight="1">
-      <c r="C260" s="2"/>
+      <c r="C260" s="3"/>
     </row>
     <row r="261" ht="15.75" customHeight="1">
-      <c r="C261" s="2"/>
+      <c r="C261" s="3"/>
     </row>
     <row r="262" ht="15.75" customHeight="1">
-      <c r="C262" s="2"/>
+      <c r="C262" s="3"/>
     </row>
     <row r="263" ht="15.75" customHeight="1">
-      <c r="C263" s="2"/>
+      <c r="C263" s="3"/>
     </row>
     <row r="264" ht="15.75" customHeight="1">
-      <c r="C264" s="2"/>
+      <c r="C264" s="3"/>
     </row>
     <row r="265" ht="15.75" customHeight="1">
-      <c r="C265" s="2"/>
+      <c r="C265" s="3"/>
     </row>
     <row r="266" ht="15.75" customHeight="1">
-      <c r="C266" s="2"/>
+      <c r="C266" s="3"/>
     </row>
     <row r="267" ht="15.75" customHeight="1">
-      <c r="C267" s="2"/>
+      <c r="C267" s="3"/>
     </row>
     <row r="268" ht="15.75" customHeight="1">
-      <c r="C268" s="2"/>
+      <c r="C268" s="3"/>
     </row>
     <row r="269" ht="15.75" customHeight="1">
-      <c r="C269" s="2"/>
+      <c r="C269" s="3"/>
     </row>
     <row r="270" ht="15.75" customHeight="1">
-      <c r="C270" s="2"/>
+      <c r="C270" s="3"/>
     </row>
     <row r="271" ht="15.75" customHeight="1">
-      <c r="C271" s="2"/>
+      <c r="C271" s="3"/>
     </row>
     <row r="272" ht="15.75" customHeight="1">
-      <c r="C272" s="2"/>
+      <c r="C272" s="3"/>
     </row>
     <row r="273" ht="15.75" customHeight="1">
-      <c r="C273" s="2"/>
+      <c r="C273" s="3"/>
     </row>
     <row r="274" ht="15.75" customHeight="1">
-      <c r="C274" s="2"/>
+      <c r="C274" s="3"/>
     </row>
     <row r="275" ht="15.75" customHeight="1">
-      <c r="C275" s="2"/>
+      <c r="C275" s="3"/>
     </row>
     <row r="276" ht="15.75" customHeight="1">
-      <c r="C276" s="2"/>
+      <c r="C276" s="3"/>
     </row>
     <row r="277" ht="15.75" customHeight="1">
-      <c r="C277" s="2"/>
+      <c r="C277" s="3"/>
     </row>
     <row r="278" ht="15.75" customHeight="1">
-      <c r="C278" s="2"/>
+      <c r="C278" s="3"/>
     </row>
     <row r="279" ht="15.75" customHeight="1">
-      <c r="C279" s="2"/>
+      <c r="C279" s="3"/>
     </row>
     <row r="280" ht="15.75" customHeight="1">
-      <c r="C280" s="2"/>
+      <c r="C280" s="3"/>
     </row>
     <row r="281" ht="15.75" customHeight="1">
-      <c r="C281" s="2"/>
+      <c r="C281" s="3"/>
     </row>
     <row r="282" ht="15.75" customHeight="1">
-      <c r="C282" s="2"/>
+      <c r="C282" s="3"/>
     </row>
     <row r="283" ht="15.75" customHeight="1">
-      <c r="C283" s="2"/>
+      <c r="C283" s="3"/>
     </row>
     <row r="284" ht="15.75" customHeight="1">
-      <c r="C284" s="2"/>
+      <c r="C284" s="3"/>
     </row>
     <row r="285" ht="15.75" customHeight="1">
-      <c r="C285" s="2"/>
+      <c r="C285" s="3"/>
     </row>
     <row r="286" ht="15.75" customHeight="1">
-      <c r="C286" s="2"/>
+      <c r="C286" s="3"/>
     </row>
     <row r="287" ht="15.75" customHeight="1">
-      <c r="C287" s="2"/>
+      <c r="C287" s="3"/>
     </row>
     <row r="288" ht="15.75" customHeight="1">
-      <c r="C288" s="2"/>
+      <c r="C288" s="3"/>
     </row>
     <row r="289" ht="15.75" customHeight="1">
-      <c r="C289" s="2"/>
+      <c r="C289" s="3"/>
     </row>
     <row r="290" ht="15.75" customHeight="1">
-      <c r="C290" s="2"/>
+      <c r="C290" s="3"/>
     </row>
     <row r="291" ht="15.75" customHeight="1">
-      <c r="C291" s="2"/>
+      <c r="C291" s="3"/>
     </row>
     <row r="292" ht="15.75" customHeight="1">
-      <c r="C292" s="2"/>
+      <c r="C292" s="3"/>
     </row>
     <row r="293" ht="15.75" customHeight="1">
-      <c r="C293" s="2"/>
+      <c r="C293" s="3"/>
     </row>
     <row r="294" ht="15.75" customHeight="1">
-      <c r="C294" s="2"/>
+      <c r="C294" s="3"/>
     </row>
     <row r="295" ht="15.75" customHeight="1">
-      <c r="C295" s="2"/>
+      <c r="C295" s="3"/>
     </row>
     <row r="296" ht="15.75" customHeight="1">
-      <c r="C296" s="2"/>
+      <c r="C296" s="3"/>
     </row>
     <row r="297" ht="15.75" customHeight="1">
-      <c r="C297" s="2"/>
+      <c r="C297" s="3"/>
     </row>
     <row r="298" ht="15.75" customHeight="1">
-      <c r="C298" s="2"/>
+      <c r="C298" s="3"/>
     </row>
     <row r="299" ht="15.75" customHeight="1">
-      <c r="C299" s="2"/>
+      <c r="C299" s="3"/>
     </row>
     <row r="300" ht="15.75" customHeight="1">
-      <c r="C300" s="2"/>
+      <c r="C300" s="3"/>
     </row>
     <row r="301" ht="15.75" customHeight="1">
-      <c r="C301" s="2"/>
+      <c r="C301" s="3"/>
     </row>
     <row r="302" ht="15.75" customHeight="1">
-      <c r="C302" s="2"/>
+      <c r="C302" s="3"/>
     </row>
     <row r="303" ht="15.75" customHeight="1">
-      <c r="C303" s="2"/>
+      <c r="C303" s="3"/>
     </row>
     <row r="304" ht="15.75" customHeight="1">
-      <c r="C304" s="2"/>
+      <c r="C304" s="3"/>
     </row>
     <row r="305" ht="15.75" customHeight="1">
-      <c r="C305" s="2"/>
+      <c r="C305" s="3"/>
     </row>
     <row r="306" ht="15.75" customHeight="1">
-      <c r="C306" s="2"/>
+      <c r="C306" s="3"/>
     </row>
     <row r="307" ht="15.75" customHeight="1">
-      <c r="C307" s="2"/>
+      <c r="C307" s="3"/>
     </row>
     <row r="308" ht="15.75" customHeight="1">
-      <c r="C308" s="2"/>
+      <c r="C308" s="3"/>
     </row>
     <row r="309" ht="15.75" customHeight="1">
-      <c r="C309" s="2"/>
+      <c r="C309" s="3"/>
     </row>
     <row r="310" ht="15.75" customHeight="1">
-      <c r="C310" s="2"/>
+      <c r="C310" s="3"/>
     </row>
     <row r="311" ht="15.75" customHeight="1">
-      <c r="C311" s="2"/>
+      <c r="C311" s="3"/>
     </row>
     <row r="312" ht="15.75" customHeight="1">
-      <c r="C312" s="2"/>
+      <c r="C312" s="3"/>
     </row>
     <row r="313" ht="15.75" customHeight="1">
-      <c r="C313" s="2"/>
+      <c r="C313" s="3"/>
     </row>
     <row r="314" ht="15.75" customHeight="1">
-      <c r="C314" s="2"/>
+      <c r="C314" s="3"/>
     </row>
     <row r="315" ht="15.75" customHeight="1">
-      <c r="C315" s="2"/>
+      <c r="C315" s="3"/>
     </row>
     <row r="316" ht="15.75" customHeight="1">
-      <c r="C316" s="2"/>
+      <c r="C316" s="3"/>
     </row>
     <row r="317" ht="15.75" customHeight="1">
-      <c r="C317" s="2"/>
+      <c r="C317" s="3"/>
     </row>
     <row r="318" ht="15.75" customHeight="1">
-      <c r="C318" s="2"/>
+      <c r="C318" s="3"/>
     </row>
     <row r="319" ht="15.75" customHeight="1">
-      <c r="C319" s="2"/>
+      <c r="C319" s="3"/>
     </row>
     <row r="320" ht="15.75" customHeight="1">
-      <c r="C320" s="2"/>
+      <c r="C320" s="3"/>
     </row>
     <row r="321" ht="15.75" customHeight="1">
-      <c r="C321" s="2"/>
+      <c r="C321" s="3"/>
     </row>
     <row r="322" ht="15.75" customHeight="1">
-      <c r="C322" s="2"/>
+      <c r="C322" s="3"/>
     </row>
     <row r="323" ht="15.75" customHeight="1">
-      <c r="C323" s="2"/>
+      <c r="C323" s="3"/>
     </row>
     <row r="324" ht="15.75" customHeight="1">
-      <c r="C324" s="2"/>
+      <c r="C324" s="3"/>
     </row>
     <row r="325" ht="15.75" customHeight="1">
-      <c r="C325" s="2"/>
+      <c r="C325" s="3"/>
     </row>
     <row r="326" ht="15.75" customHeight="1">
-      <c r="C326" s="2"/>
+      <c r="C326" s="3"/>
     </row>
     <row r="327" ht="15.75" customHeight="1">
-      <c r="C327" s="2"/>
+      <c r="C327" s="3"/>
     </row>
     <row r="328" ht="15.75" customHeight="1">
-      <c r="C328" s="2"/>
+      <c r="C328" s="3"/>
     </row>
     <row r="329" ht="15.75" customHeight="1">
-      <c r="C329" s="2"/>
+      <c r="C329" s="3"/>
     </row>
     <row r="330" ht="15.75" customHeight="1">
-      <c r="C330" s="2"/>
+      <c r="C330" s="3"/>
     </row>
     <row r="331" ht="15.75" customHeight="1">
-      <c r="C331" s="2"/>
+      <c r="C331" s="3"/>
     </row>
     <row r="332" ht="15.75" customHeight="1">
-      <c r="C332" s="2"/>
+      <c r="C332" s="3"/>
     </row>
     <row r="333" ht="15.75" customHeight="1">
-      <c r="C333" s="2"/>
+      <c r="C333" s="3"/>
     </row>
     <row r="334" ht="15.75" customHeight="1">
-      <c r="C334" s="2"/>
+      <c r="C334" s="3"/>
     </row>
     <row r="335" ht="15.75" customHeight="1">
-      <c r="C335" s="2"/>
+      <c r="C335" s="3"/>
     </row>
     <row r="336" ht="15.75" customHeight="1">
-      <c r="C336" s="2"/>
+      <c r="C336" s="3"/>
     </row>
     <row r="337" ht="15.75" customHeight="1">
-      <c r="C337" s="2"/>
+      <c r="C337" s="3"/>
     </row>
     <row r="338" ht="15.75" customHeight="1">
-      <c r="C338" s="2"/>
+      <c r="C338" s="3"/>
     </row>
     <row r="339" ht="15.75" customHeight="1">
-      <c r="C339" s="2"/>
+      <c r="C339" s="3"/>
     </row>
     <row r="340" ht="15.75" customHeight="1">
-      <c r="C340" s="2"/>
+      <c r="C340" s="3"/>
     </row>
     <row r="341" ht="15.75" customHeight="1">
-      <c r="C341" s="2"/>
+      <c r="C341" s="3"/>
     </row>
     <row r="342" ht="15.75" customHeight="1">
-      <c r="C342" s="2"/>
+      <c r="C342" s="3"/>
     </row>
     <row r="343" ht="15.75" customHeight="1">
-      <c r="C343" s="2"/>
+      <c r="C343" s="3"/>
     </row>
     <row r="344" ht="15.75" customHeight="1">
-      <c r="C344" s="2"/>
+      <c r="C344" s="3"/>
     </row>
     <row r="345" ht="15.75" customHeight="1">
-      <c r="C345" s="2"/>
+      <c r="C345" s="3"/>
     </row>
     <row r="346" ht="15.75" customHeight="1">
-      <c r="C346" s="2"/>
+      <c r="C346" s="3"/>
     </row>
     <row r="347" ht="15.75" customHeight="1">
-      <c r="C347" s="2"/>
+      <c r="C347" s="3"/>
     </row>
     <row r="348" ht="15.75" customHeight="1">
-      <c r="C348" s="2"/>
+      <c r="C348" s="3"/>
     </row>
     <row r="349" ht="15.75" customHeight="1">
-      <c r="C349" s="2"/>
+      <c r="C349" s="3"/>
     </row>
     <row r="350" ht="15.75" customHeight="1">
-      <c r="C350" s="2"/>
+      <c r="C350" s="3"/>
     </row>
     <row r="351" ht="15.75" customHeight="1">
-      <c r="C351" s="2"/>
+      <c r="C351" s="3"/>
     </row>
     <row r="352" ht="15.75" customHeight="1">
-      <c r="C352" s="2"/>
+      <c r="C352" s="3"/>
     </row>
     <row r="353" ht="15.75" customHeight="1">
-      <c r="C353" s="2"/>
+      <c r="C353" s="3"/>
     </row>
     <row r="354" ht="15.75" customHeight="1">
-      <c r="C354" s="2"/>
+      <c r="C354" s="3"/>
     </row>
     <row r="355" ht="15.75" customHeight="1">
-      <c r="C355" s="2"/>
+      <c r="C355" s="3"/>
     </row>
     <row r="356" ht="15.75" customHeight="1">
-      <c r="C356" s="2"/>
+      <c r="C356" s="3"/>
     </row>
     <row r="357" ht="15.75" customHeight="1">
-      <c r="C357" s="2"/>
+      <c r="C357" s="3"/>
     </row>
     <row r="358" ht="15.75" customHeight="1">
-      <c r="C358" s="2"/>
+      <c r="C358" s="3"/>
     </row>
     <row r="359" ht="15.75" customHeight="1">
-      <c r="C359" s="2"/>
+      <c r="C359" s="3"/>
     </row>
     <row r="360" ht="15.75" customHeight="1">
-      <c r="C360" s="2"/>
+      <c r="C360" s="3"/>
     </row>
     <row r="361" ht="15.75" customHeight="1">
-      <c r="C361" s="2"/>
+      <c r="C361" s="3"/>
     </row>
     <row r="362" ht="15.75" customHeight="1">
-      <c r="C362" s="2"/>
+      <c r="C362" s="3"/>
     </row>
     <row r="363" ht="15.75" customHeight="1">
-      <c r="C363" s="2"/>
+      <c r="C363" s="3"/>
     </row>
     <row r="364" ht="15.75" customHeight="1">
-      <c r="C364" s="2"/>
+      <c r="C364" s="3"/>
     </row>
     <row r="365" ht="15.75" customHeight="1">
-      <c r="C365" s="2"/>
+      <c r="C365" s="3"/>
     </row>
     <row r="366" ht="15.75" customHeight="1">
-      <c r="C366" s="2"/>
+      <c r="C366" s="3"/>
     </row>
     <row r="367" ht="15.75" customHeight="1">
-      <c r="C367" s="2"/>
+      <c r="C367" s="3"/>
     </row>
     <row r="368" ht="15.75" customHeight="1">
-      <c r="C368" s="2"/>
+      <c r="C368" s="3"/>
     </row>
     <row r="369" ht="15.75" customHeight="1">
-      <c r="C369" s="2"/>
+      <c r="C369" s="3"/>
     </row>
     <row r="370" ht="15.75" customHeight="1">
-      <c r="C370" s="2"/>
+      <c r="C370" s="3"/>
     </row>
     <row r="371" ht="15.75" customHeight="1">
-      <c r="C371" s="2"/>
+      <c r="C371" s="3"/>
     </row>
     <row r="372" ht="15.75" customHeight="1">
-      <c r="C372" s="2"/>
+      <c r="C372" s="3"/>
     </row>
     <row r="373" ht="15.75" customHeight="1">
-      <c r="C373" s="2"/>
+      <c r="C373" s="3"/>
     </row>
     <row r="374" ht="15.75" customHeight="1">
-      <c r="C374" s="2"/>
+      <c r="C374" s="3"/>
     </row>
     <row r="375" ht="15.75" customHeight="1">
-      <c r="C375" s="2"/>
+      <c r="C375" s="3"/>
     </row>
     <row r="376" ht="15.75" customHeight="1">
-      <c r="C376" s="2"/>
+      <c r="C376" s="3"/>
     </row>
     <row r="377" ht="15.75" customHeight="1">
-      <c r="C377" s="2"/>
+      <c r="C377" s="3"/>
     </row>
     <row r="378" ht="15.75" customHeight="1">
-      <c r="C378" s="2"/>
+      <c r="C378" s="3"/>
     </row>
     <row r="379" ht="15.75" customHeight="1">
-      <c r="C379" s="2"/>
+      <c r="C379" s="3"/>
     </row>
     <row r="380" ht="15.75" customHeight="1">
-      <c r="C380" s="2"/>
+      <c r="C380" s="3"/>
     </row>
     <row r="381" ht="15.75" customHeight="1">
-      <c r="C381" s="2"/>
+      <c r="C381" s="3"/>
     </row>
     <row r="382" ht="15.75" customHeight="1">
-      <c r="C382" s="2"/>
+      <c r="C382" s="3"/>
     </row>
     <row r="383" ht="15.75" customHeight="1">
-      <c r="C383" s="2"/>
+      <c r="C383" s="3"/>
     </row>
     <row r="384" ht="15.75" customHeight="1">
-      <c r="C384" s="2"/>
+      <c r="C384" s="3"/>
     </row>
     <row r="385" ht="15.75" customHeight="1">
-      <c r="C385" s="2"/>
+      <c r="C385" s="3"/>
     </row>
     <row r="386" ht="15.75" customHeight="1">
-      <c r="C386" s="2"/>
+      <c r="C386" s="3"/>
     </row>
     <row r="387" ht="15.75" customHeight="1">
-      <c r="C387" s="2"/>
+      <c r="C387" s="3"/>
     </row>
     <row r="388" ht="15.75" customHeight="1">
-      <c r="C388" s="2"/>
+      <c r="C388" s="3"/>
     </row>
     <row r="389" ht="15.75" customHeight="1">
-      <c r="C389" s="2"/>
+      <c r="C389" s="3"/>
     </row>
     <row r="390" ht="15.75" customHeight="1">
-      <c r="C390" s="2"/>
+      <c r="C390" s="3"/>
     </row>
     <row r="391" ht="15.75" customHeight="1">
-      <c r="C391" s="2"/>
+      <c r="C391" s="3"/>
     </row>
     <row r="392" ht="15.75" customHeight="1">
-      <c r="C392" s="2"/>
+      <c r="C392" s="3"/>
     </row>
     <row r="393" ht="15.75" customHeight="1">
-      <c r="C393" s="2"/>
+      <c r="C393" s="3"/>
     </row>
     <row r="394" ht="15.75" customHeight="1">
-      <c r="C394" s="2"/>
+      <c r="C394" s="3"/>
     </row>
     <row r="395" ht="15.75" customHeight="1">
-      <c r="C395" s="2"/>
+      <c r="C395" s="3"/>
     </row>
     <row r="396" ht="15.75" customHeight="1">
-      <c r="C396" s="2"/>
+      <c r="C396" s="3"/>
     </row>
     <row r="397" ht="15.75" customHeight="1">
-      <c r="C397" s="2"/>
+      <c r="C397" s="3"/>
     </row>
     <row r="398" ht="15.75" customHeight="1">
-      <c r="C398" s="2"/>
+      <c r="C398" s="3"/>
     </row>
     <row r="399" ht="15.75" customHeight="1">
-      <c r="C399" s="2"/>
+      <c r="C399" s="3"/>
     </row>
     <row r="400" ht="15.75" customHeight="1">
-      <c r="C400" s="2"/>
+      <c r="C400" s="3"/>
     </row>
     <row r="401" ht="15.75" customHeight="1">
-      <c r="C401" s="2"/>
+      <c r="C401" s="3"/>
     </row>
     <row r="402" ht="15.75" customHeight="1">
-      <c r="C402" s="2"/>
+      <c r="C402" s="3"/>
     </row>
     <row r="403" ht="15.75" customHeight="1">
-      <c r="C403" s="2"/>
+      <c r="C403" s="3"/>
     </row>
     <row r="404" ht="15.75" customHeight="1">
-      <c r="C404" s="2"/>
+      <c r="C404" s="3"/>
     </row>
     <row r="405" ht="15.75" customHeight="1">
-      <c r="C405" s="2"/>
+      <c r="C405" s="3"/>
     </row>
     <row r="406" ht="15.75" customHeight="1">
-      <c r="C406" s="2"/>
+      <c r="C406" s="3"/>
     </row>
     <row r="407" ht="15.75" customHeight="1">
-      <c r="C407" s="2"/>
+      <c r="C407" s="3"/>
     </row>
     <row r="408" ht="15.75" customHeight="1">
-      <c r="C408" s="2"/>
+      <c r="C408" s="3"/>
     </row>
     <row r="409" ht="15.75" customHeight="1">
-      <c r="C409" s="2"/>
+      <c r="C409" s="3"/>
     </row>
     <row r="410" ht="15.75" customHeight="1">
-      <c r="C410" s="2"/>
+      <c r="C410" s="3"/>
     </row>
     <row r="411" ht="15.75" customHeight="1">
-      <c r="C411" s="2"/>
+      <c r="C411" s="3"/>
     </row>
     <row r="412" ht="15.75" customHeight="1">
-      <c r="C412" s="2"/>
+      <c r="C412" s="3"/>
     </row>
     <row r="413" ht="15.75" customHeight="1">
-      <c r="C413" s="2"/>
+      <c r="C413" s="3"/>
     </row>
     <row r="414" ht="15.75" customHeight="1">
-      <c r="C414" s="2"/>
+      <c r="C414" s="3"/>
     </row>
     <row r="415" ht="15.75" customHeight="1">
-      <c r="C415" s="2"/>
+      <c r="C415" s="3"/>
     </row>
     <row r="416" ht="15.75" customHeight="1">
-      <c r="C416" s="2"/>
+      <c r="C416" s="3"/>
     </row>
     <row r="417" ht="15.75" customHeight="1">
-      <c r="C417" s="2"/>
+      <c r="C417" s="3"/>
     </row>
     <row r="418" ht="15.75" customHeight="1">
-      <c r="C418" s="2"/>
+      <c r="C418" s="3"/>
     </row>
     <row r="419" ht="15.75" customHeight="1">
-      <c r="C419" s="2"/>
+      <c r="C419" s="3"/>
     </row>
     <row r="420" ht="15.75" customHeight="1">
-      <c r="C420" s="2"/>
+      <c r="C420" s="3"/>
     </row>
     <row r="421" ht="15.75" customHeight="1">
-      <c r="C421" s="2"/>
+      <c r="C421" s="3"/>
     </row>
     <row r="422" ht="15.75" customHeight="1">
-      <c r="C422" s="2"/>
+      <c r="C422" s="3"/>
     </row>
     <row r="423" ht="15.75" customHeight="1">
-      <c r="C423" s="2"/>
+      <c r="C423" s="3"/>
     </row>
     <row r="424" ht="15.75" customHeight="1">
-      <c r="C424" s="2"/>
+      <c r="C424" s="3"/>
     </row>
     <row r="425" ht="15.75" customHeight="1">
-      <c r="C425" s="2"/>
+      <c r="C425" s="3"/>
     </row>
     <row r="426" ht="15.75" customHeight="1">
-      <c r="C426" s="2"/>
+      <c r="C426" s="3"/>
     </row>
     <row r="427" ht="15.75" customHeight="1">
-      <c r="C427" s="2"/>
+      <c r="C427" s="3"/>
     </row>
     <row r="428" ht="15.75" customHeight="1">
-      <c r="C428" s="2"/>
+      <c r="C428" s="3"/>
     </row>
     <row r="429" ht="15.75" customHeight="1">
-      <c r="C429" s="2"/>
+      <c r="C429" s="3"/>
     </row>
     <row r="430" ht="15.75" customHeight="1">
-      <c r="C430" s="2"/>
+      <c r="C430" s="3"/>
     </row>
     <row r="431" ht="15.75" customHeight="1">
-      <c r="C431" s="2"/>
+      <c r="C431" s="3"/>
     </row>
     <row r="432" ht="15.75" customHeight="1">
-      <c r="C432" s="2"/>
+      <c r="C432" s="3"/>
     </row>
     <row r="433" ht="15.75" customHeight="1">
-      <c r="C433" s="2"/>
+      <c r="C433" s="3"/>
     </row>
     <row r="434" ht="15.75" customHeight="1">
-      <c r="C434" s="2"/>
+      <c r="C434" s="3"/>
     </row>
     <row r="435" ht="15.75" customHeight="1">
-      <c r="C435" s="2"/>
+      <c r="C435" s="3"/>
     </row>
     <row r="436" ht="15.75" customHeight="1">
-      <c r="C436" s="2"/>
+      <c r="C436" s="3"/>
     </row>
     <row r="437" ht="15.75" customHeight="1">
-      <c r="C437" s="2"/>
+      <c r="C437" s="3"/>
     </row>
     <row r="438" ht="15.75" customHeight="1">
-      <c r="C438" s="2"/>
+      <c r="C438" s="3"/>
     </row>
     <row r="439" ht="15.75" customHeight="1">
-      <c r="C439" s="2"/>
+      <c r="C439" s="3"/>
     </row>
     <row r="440" ht="15.75" customHeight="1">
-      <c r="C440" s="2"/>
+      <c r="C440" s="3"/>
     </row>
     <row r="441" ht="15.75" customHeight="1">
-      <c r="C441" s="2"/>
+      <c r="C441" s="3"/>
     </row>
     <row r="442" ht="15.75" customHeight="1">
-      <c r="C442" s="2"/>
+      <c r="C442" s="3"/>
     </row>
     <row r="443" ht="15.75" customHeight="1">
-      <c r="C443" s="2"/>
+      <c r="C443" s="3"/>
     </row>
     <row r="444" ht="15.75" customHeight="1">
-      <c r="C444" s="2"/>
+      <c r="C444" s="3"/>
     </row>
     <row r="445" ht="15.75" customHeight="1">
-      <c r="C445" s="2"/>
+      <c r="C445" s="3"/>
     </row>
     <row r="446" ht="15.75" customHeight="1">
-      <c r="C446" s="2"/>
+      <c r="C446" s="3"/>
     </row>
     <row r="447" ht="15.75" customHeight="1">
-      <c r="C447" s="2"/>
+      <c r="C447" s="3"/>
     </row>
     <row r="448" ht="15.75" customHeight="1">
-      <c r="C448" s="2"/>
+      <c r="C448" s="3"/>
     </row>
     <row r="449" ht="15.75" customHeight="1">
-      <c r="C449" s="2"/>
+      <c r="C449" s="3"/>
     </row>
     <row r="450" ht="15.75" customHeight="1">
-      <c r="C450" s="2"/>
+      <c r="C450" s="3"/>
     </row>
     <row r="451" ht="15.75" customHeight="1">
-      <c r="C451" s="2"/>
+      <c r="C451" s="3"/>
     </row>
     <row r="452" ht="15.75" customHeight="1">
-      <c r="C452" s="2"/>
+      <c r="C452" s="3"/>
     </row>
     <row r="453" ht="15.75" customHeight="1">
-      <c r="C453" s="2"/>
+      <c r="C453" s="3"/>
     </row>
     <row r="454" ht="15.75" customHeight="1">
-      <c r="C454" s="2"/>
+      <c r="C454" s="3"/>
     </row>
     <row r="455" ht="15.75" customHeight="1">
-      <c r="C455" s="2"/>
+      <c r="C455" s="3"/>
     </row>
     <row r="456" ht="15.75" customHeight="1">
-      <c r="C456" s="2"/>
+      <c r="C456" s="3"/>
     </row>
     <row r="457" ht="15.75" customHeight="1">
-      <c r="C457" s="2"/>
+      <c r="C457" s="3"/>
     </row>
     <row r="458" ht="15.75" customHeight="1">
-      <c r="C458" s="2"/>
+      <c r="C458" s="3"/>
     </row>
     <row r="459" ht="15.75" customHeight="1">
-      <c r="C459" s="2"/>
+      <c r="C459" s="3"/>
     </row>
     <row r="460" ht="15.75" customHeight="1">
-      <c r="C460" s="2"/>
+      <c r="C460" s="3"/>
     </row>
     <row r="461" ht="15.75" customHeight="1">
-      <c r="C461" s="2"/>
+      <c r="C461" s="3"/>
     </row>
     <row r="462" ht="15.75" customHeight="1">
-      <c r="C462" s="2"/>
+      <c r="C462" s="3"/>
     </row>
     <row r="463" ht="15.75" customHeight="1">
-      <c r="C463" s="2"/>
+      <c r="C463" s="3"/>
     </row>
     <row r="464" ht="15.75" customHeight="1">
-      <c r="C464" s="2"/>
+      <c r="C464" s="3"/>
     </row>
     <row r="465" ht="15.75" customHeight="1">
-      <c r="C465" s="2"/>
+      <c r="C465" s="3"/>
     </row>
     <row r="466" ht="15.75" customHeight="1">
-      <c r="C466" s="2"/>
+      <c r="C466" s="3"/>
     </row>
     <row r="467" ht="15.75" customHeight="1">
-      <c r="C467" s="2"/>
+      <c r="C467" s="3"/>
     </row>
     <row r="468" ht="15.75" customHeight="1">
-      <c r="C468" s="2"/>
+      <c r="C468" s="3"/>
     </row>
     <row r="469" ht="15.75" customHeight="1">
-      <c r="C469" s="2"/>
+      <c r="C469" s="3"/>
     </row>
     <row r="470" ht="15.75" customHeight="1">
-      <c r="C470" s="2"/>
+      <c r="C470" s="3"/>
     </row>
     <row r="471" ht="15.75" customHeight="1">
-      <c r="C471" s="2"/>
+      <c r="C471" s="3"/>
     </row>
     <row r="472" ht="15.75" customHeight="1">
-      <c r="C472" s="2"/>
+      <c r="C472" s="3"/>
     </row>
     <row r="473" ht="15.75" customHeight="1">
-      <c r="C473" s="2"/>
+      <c r="C473" s="3"/>
     </row>
     <row r="474" ht="15.75" customHeight="1">
-      <c r="C474" s="2"/>
+      <c r="C474" s="3"/>
     </row>
     <row r="475" ht="15.75" customHeight="1">
-      <c r="C475" s="2"/>
+      <c r="C475" s="3"/>
     </row>
     <row r="476" ht="15.75" customHeight="1">
-      <c r="C476" s="2"/>
+      <c r="C476" s="3"/>
     </row>
     <row r="477" ht="15.75" customHeight="1">
-      <c r="C477" s="2"/>
+      <c r="C477" s="3"/>
     </row>
     <row r="478" ht="15.75" customHeight="1">
-      <c r="C478" s="2"/>
+      <c r="C478" s="3"/>
     </row>
     <row r="479" ht="15.75" customHeight="1">
-      <c r="C479" s="2"/>
+      <c r="C479" s="3"/>
     </row>
     <row r="480" ht="15.75" customHeight="1">
-      <c r="C480" s="2"/>
+      <c r="C480" s="3"/>
     </row>
     <row r="481" ht="15.75" customHeight="1">
-      <c r="C481" s="2"/>
+      <c r="C481" s="3"/>
     </row>
     <row r="482" ht="15.75" customHeight="1">
-      <c r="C482" s="2"/>
+      <c r="C482" s="3"/>
     </row>
     <row r="483" ht="15.75" customHeight="1">
-      <c r="C483" s="2"/>
+      <c r="C483" s="3"/>
     </row>
     <row r="484" ht="15.75" customHeight="1">
-      <c r="C484" s="2"/>
+      <c r="C484" s="3"/>
     </row>
     <row r="485" ht="15.75" customHeight="1">
-      <c r="C485" s="2"/>
+      <c r="C485" s="3"/>
     </row>
     <row r="486" ht="15.75" customHeight="1">
-      <c r="C486" s="2"/>
+      <c r="C486" s="3"/>
     </row>
     <row r="487" ht="15.75" customHeight="1">
-      <c r="C487" s="2"/>
+      <c r="C487" s="3"/>
     </row>
     <row r="488" ht="15.75" customHeight="1">
-      <c r="C488" s="2"/>
+      <c r="C488" s="3"/>
     </row>
     <row r="489" ht="15.75" customHeight="1">
-      <c r="C489" s="2"/>
+      <c r="C489" s="3"/>
     </row>
     <row r="490" ht="15.75" customHeight="1">
-      <c r="C490" s="2"/>
+      <c r="C490" s="3"/>
     </row>
     <row r="491" ht="15.75" customHeight="1">
-      <c r="C491" s="2"/>
+      <c r="C491" s="3"/>
     </row>
     <row r="492" ht="15.75" customHeight="1">
-      <c r="C492" s="2"/>
+      <c r="C492" s="3"/>
     </row>
     <row r="493" ht="15.75" customHeight="1">
-      <c r="C493" s="2"/>
+      <c r="C493" s="3"/>
     </row>
     <row r="494" ht="15.75" customHeight="1">
-      <c r="C494" s="2"/>
+      <c r="C494" s="3"/>
     </row>
     <row r="495" ht="15.75" customHeight="1">
-      <c r="C495" s="2"/>
+      <c r="C495" s="3"/>
     </row>
     <row r="496" ht="15.75" customHeight="1">
-      <c r="C496" s="2"/>
+      <c r="C496" s="3"/>
     </row>
     <row r="497" ht="15.75" customHeight="1">
-      <c r="C497" s="2"/>
+      <c r="C497" s="3"/>
     </row>
     <row r="498" ht="15.75" customHeight="1">
-      <c r="C498" s="2"/>
+      <c r="C498" s="3"/>
     </row>
     <row r="499" ht="15.75" customHeight="1">
-      <c r="C499" s="2"/>
+      <c r="C499" s="3"/>
     </row>
     <row r="500" ht="15.75" customHeight="1">
-      <c r="C500" s="2"/>
+      <c r="C500" s="3"/>
     </row>
     <row r="501" ht="15.75" customHeight="1">
-      <c r="C501" s="2"/>
+      <c r="C501" s="3"/>
     </row>
     <row r="502" ht="15.75" customHeight="1">
-      <c r="C502" s="2"/>
+      <c r="C502" s="3"/>
     </row>
     <row r="503" ht="15.75" customHeight="1">
-      <c r="C503" s="2"/>
+      <c r="C503" s="3"/>
     </row>
     <row r="504" ht="15.75" customHeight="1">
-      <c r="C504" s="2"/>
+      <c r="C504" s="3"/>
     </row>
     <row r="505" ht="15.75" customHeight="1">
-      <c r="C505" s="2"/>
+      <c r="C505" s="3"/>
     </row>
     <row r="506" ht="15.75" customHeight="1">
-      <c r="C506" s="2"/>
+      <c r="C506" s="3"/>
     </row>
     <row r="507" ht="15.75" customHeight="1">
-      <c r="C507" s="2"/>
+      <c r="C507" s="3"/>
     </row>
     <row r="508" ht="15.75" customHeight="1">
-      <c r="C508" s="2"/>
+      <c r="C508" s="3"/>
     </row>
     <row r="509" ht="15.75" customHeight="1">
-      <c r="C509" s="2"/>
+      <c r="C509" s="3"/>
     </row>
     <row r="510" ht="15.75" customHeight="1">
-      <c r="C510" s="2"/>
+      <c r="C510" s="3"/>
     </row>
     <row r="511" ht="15.75" customHeight="1">
-      <c r="C511" s="2"/>
+      <c r="C511" s="3"/>
     </row>
     <row r="512" ht="15.75" customHeight="1">
-      <c r="C512" s="2"/>
+      <c r="C512" s="3"/>
     </row>
     <row r="513" ht="15.75" customHeight="1">
-      <c r="C513" s="2"/>
+      <c r="C513" s="3"/>
     </row>
     <row r="514" ht="15.75" customHeight="1">
-      <c r="C514" s="2"/>
+      <c r="C514" s="3"/>
     </row>
     <row r="515" ht="15.75" customHeight="1">
-      <c r="C515" s="2"/>
+      <c r="C515" s="3"/>
     </row>
     <row r="516" ht="15.75" customHeight="1">
-      <c r="C516" s="2"/>
+      <c r="C516" s="3"/>
     </row>
     <row r="517" ht="15.75" customHeight="1">
-      <c r="C517" s="2"/>
+      <c r="C517" s="3"/>
     </row>
     <row r="518" ht="15.75" customHeight="1">
-      <c r="C518" s="2"/>
+      <c r="C518" s="3"/>
     </row>
     <row r="519" ht="15.75" customHeight="1">
-      <c r="C519" s="2"/>
+      <c r="C519" s="3"/>
     </row>
     <row r="520" ht="15.75" customHeight="1">
-      <c r="C520" s="2"/>
+      <c r="C520" s="3"/>
     </row>
     <row r="521" ht="15.75" customHeight="1">
-      <c r="C521" s="2"/>
+      <c r="C521" s="3"/>
     </row>
     <row r="522" ht="15.75" customHeight="1">
-      <c r="C522" s="2"/>
+      <c r="C522" s="3"/>
     </row>
     <row r="523" ht="15.75" customHeight="1">
-      <c r="C523" s="2"/>
+      <c r="C523" s="3"/>
     </row>
     <row r="524" ht="15.75" customHeight="1">
-      <c r="C524" s="2"/>
+      <c r="C524" s="3"/>
     </row>
     <row r="525" ht="15.75" customHeight="1">
-      <c r="C525" s="2"/>
+      <c r="C525" s="3"/>
     </row>
     <row r="526" ht="15.75" customHeight="1">
-      <c r="C526" s="2"/>
+      <c r="C526" s="3"/>
     </row>
     <row r="527" ht="15.75" customHeight="1">
-      <c r="C527" s="2"/>
+      <c r="C527" s="3"/>
     </row>
     <row r="528" ht="15.75" customHeight="1">
-      <c r="C528" s="2"/>
+      <c r="C528" s="3"/>
     </row>
     <row r="529" ht="15.75" customHeight="1">
-      <c r="C529" s="2"/>
+      <c r="C529" s="3"/>
     </row>
     <row r="530" ht="15.75" customHeight="1">
-      <c r="C530" s="2"/>
+      <c r="C530" s="3"/>
     </row>
     <row r="531" ht="15.75" customHeight="1">
-      <c r="C531" s="2"/>
+      <c r="C531" s="3"/>
     </row>
     <row r="532" ht="15.75" customHeight="1">
-      <c r="C532" s="2"/>
+      <c r="C532" s="3"/>
     </row>
     <row r="533" ht="15.75" customHeight="1">
-      <c r="C533" s="2"/>
+      <c r="C533" s="3"/>
     </row>
     <row r="534" ht="15.75" customHeight="1">
-      <c r="C534" s="2"/>
+      <c r="C534" s="3"/>
     </row>
     <row r="535" ht="15.75" customHeight="1">
-      <c r="C535" s="2"/>
+      <c r="C535" s="3"/>
     </row>
     <row r="536" ht="15.75" customHeight="1">
-      <c r="C536" s="2"/>
+      <c r="C536" s="3"/>
     </row>
     <row r="537" ht="15.75" customHeight="1">
-      <c r="C537" s="2"/>
+      <c r="C537" s="3"/>
     </row>
     <row r="538" ht="15.75" customHeight="1">
-      <c r="C538" s="2"/>
+      <c r="C538" s="3"/>
     </row>
     <row r="539" ht="15.75" customHeight="1">
-      <c r="C539" s="2"/>
+      <c r="C539" s="3"/>
     </row>
     <row r="540" ht="15.75" customHeight="1">
-      <c r="C540" s="2"/>
+      <c r="C540" s="3"/>
     </row>
     <row r="541" ht="15.75" customHeight="1">
-      <c r="C541" s="2"/>
+      <c r="C541" s="3"/>
     </row>
     <row r="542" ht="15.75" customHeight="1">
-      <c r="C542" s="2"/>
+      <c r="C542" s="3"/>
     </row>
     <row r="543" ht="15.75" customHeight="1">
-      <c r="C543" s="2"/>
+      <c r="C543" s="3"/>
     </row>
     <row r="544" ht="15.75" customHeight="1">
-      <c r="C544" s="2"/>
+      <c r="C544" s="3"/>
     </row>
     <row r="545" ht="15.75" customHeight="1">
-      <c r="C545" s="2"/>
+      <c r="C545" s="3"/>
     </row>
     <row r="546" ht="15.75" customHeight="1">
-      <c r="C546" s="2"/>
+      <c r="C546" s="3"/>
     </row>
     <row r="547" ht="15.75" customHeight="1">
-      <c r="C547" s="2"/>
+      <c r="C547" s="3"/>
     </row>
     <row r="548" ht="15.75" customHeight="1">
-      <c r="C548" s="2"/>
+      <c r="C548" s="3"/>
     </row>
     <row r="549" ht="15.75" customHeight="1">
-      <c r="C549" s="2"/>
+      <c r="C549" s="3"/>
     </row>
     <row r="550" ht="15.75" customHeight="1">
-      <c r="C550" s="2"/>
+      <c r="C550" s="3"/>
     </row>
     <row r="551" ht="15.75" customHeight="1">
-      <c r="C551" s="2"/>
+      <c r="C551" s="3"/>
     </row>
     <row r="552" ht="15.75" customHeight="1">
-      <c r="C552" s="2"/>
+      <c r="C552" s="3"/>
     </row>
     <row r="553" ht="15.75" customHeight="1">
-      <c r="C553" s="2"/>
+      <c r="C553" s="3"/>
     </row>
     <row r="554" ht="15.75" customHeight="1">
-      <c r="C554" s="2"/>
+      <c r="C554" s="3"/>
     </row>
     <row r="555" ht="15.75" customHeight="1">
-      <c r="C555" s="2"/>
+      <c r="C555" s="3"/>
     </row>
     <row r="556" ht="15.75" customHeight="1">
-      <c r="C556" s="2"/>
+      <c r="C556" s="3"/>
     </row>
     <row r="557" ht="15.75" customHeight="1">
-      <c r="C557" s="2"/>
+      <c r="C557" s="3"/>
     </row>
     <row r="558" ht="15.75" customHeight="1">
-      <c r="C558" s="2"/>
+      <c r="C558" s="3"/>
     </row>
     <row r="559" ht="15.75" customHeight="1">
-      <c r="C559" s="2"/>
+      <c r="C559" s="3"/>
     </row>
     <row r="560" ht="15.75" customHeight="1">
-      <c r="C560" s="2"/>
+      <c r="C560" s="3"/>
     </row>
     <row r="561" ht="15.75" customHeight="1">
-      <c r="C561" s="2"/>
+      <c r="C561" s="3"/>
     </row>
     <row r="562" ht="15.75" customHeight="1">
-      <c r="C562" s="2"/>
+      <c r="C562" s="3"/>
     </row>
     <row r="563" ht="15.75" customHeight="1">
-      <c r="C563" s="2"/>
+      <c r="C563" s="3"/>
     </row>
     <row r="564" ht="15.75" customHeight="1">
-      <c r="C564" s="2"/>
+      <c r="C564" s="3"/>
     </row>
     <row r="565" ht="15.75" customHeight="1">
-      <c r="C565" s="2"/>
+      <c r="C565" s="3"/>
     </row>
     <row r="566" ht="15.75" customHeight="1">
-      <c r="C566" s="2"/>
+      <c r="C566" s="3"/>
     </row>
     <row r="567" ht="15.75" customHeight="1">
-      <c r="C567" s="2"/>
+      <c r="C567" s="3"/>
     </row>
     <row r="568" ht="15.75" customHeight="1">
-      <c r="C568" s="2"/>
+      <c r="C568" s="3"/>
     </row>
     <row r="569" ht="15.75" customHeight="1">
-      <c r="C569" s="2"/>
+      <c r="C569" s="3"/>
     </row>
     <row r="570" ht="15.75" customHeight="1">
-      <c r="C570" s="2"/>
+      <c r="C570" s="3"/>
     </row>
     <row r="571" ht="15.75" customHeight="1">
-      <c r="C571" s="2"/>
+      <c r="C571" s="3"/>
     </row>
     <row r="572" ht="15.75" customHeight="1">
-      <c r="C572" s="2"/>
+      <c r="C572" s="3"/>
     </row>
     <row r="573" ht="15.75" customHeight="1">
-      <c r="C573" s="2"/>
+      <c r="C573" s="3"/>
     </row>
     <row r="574" ht="15.75" customHeight="1">
-      <c r="C574" s="2"/>
+      <c r="C574" s="3"/>
     </row>
     <row r="575" ht="15.75" customHeight="1">
-      <c r="C575" s="2"/>
+      <c r="C575" s="3"/>
     </row>
     <row r="576" ht="15.75" customHeight="1">
-      <c r="C576" s="2"/>
+      <c r="C576" s="3"/>
     </row>
     <row r="577" ht="15.75" customHeight="1">
-      <c r="C577" s="2"/>
+      <c r="C577" s="3"/>
     </row>
     <row r="578" ht="15.75" customHeight="1">
-      <c r="C578" s="2"/>
+      <c r="C578" s="3"/>
     </row>
     <row r="579" ht="15.75" customHeight="1">
-      <c r="C579" s="2"/>
+      <c r="C579" s="3"/>
     </row>
     <row r="580" ht="15.75" customHeight="1">
-      <c r="C580" s="2"/>
+      <c r="C580" s="3"/>
     </row>
     <row r="581" ht="15.75" customHeight="1">
-      <c r="C581" s="2"/>
+      <c r="C581" s="3"/>
     </row>
     <row r="582" ht="15.75" customHeight="1">
-      <c r="C582" s="2"/>
+      <c r="C582" s="3"/>
     </row>
     <row r="583" ht="15.75" customHeight="1">
-      <c r="C583" s="2"/>
+      <c r="C583" s="3"/>
     </row>
     <row r="584" ht="15.75" customHeight="1">
-      <c r="C584" s="2"/>
+      <c r="C584" s="3"/>
     </row>
     <row r="585" ht="15.75" customHeight="1">
-      <c r="C585" s="2"/>
+      <c r="C585" s="3"/>
     </row>
     <row r="586" ht="15.75" customHeight="1">
-      <c r="C586" s="2"/>
+      <c r="C586" s="3"/>
     </row>
     <row r="587" ht="15.75" customHeight="1">
-      <c r="C587" s="2"/>
+      <c r="C587" s="3"/>
     </row>
     <row r="588" ht="15.75" customHeight="1">
-      <c r="C588" s="2"/>
+      <c r="C588" s="3"/>
     </row>
     <row r="589" ht="15.75" customHeight="1">
-      <c r="C589" s="2"/>
+      <c r="C589" s="3"/>
     </row>
     <row r="590" ht="15.75" customHeight="1">
-      <c r="C590" s="2"/>
+      <c r="C590" s="3"/>
     </row>
     <row r="591" ht="15.75" customHeight="1">
-      <c r="C591" s="2"/>
+      <c r="C591" s="3"/>
     </row>
     <row r="592" ht="15.75" customHeight="1">
-      <c r="C592" s="2"/>
+      <c r="C592" s="3"/>
     </row>
     <row r="593" ht="15.75" customHeight="1">
-      <c r="C593" s="2"/>
+      <c r="C593" s="3"/>
     </row>
     <row r="594" ht="15.75" customHeight="1">
-      <c r="C594" s="2"/>
+      <c r="C594" s="3"/>
     </row>
     <row r="595" ht="15.75" customHeight="1">
-      <c r="C595" s="2"/>
+      <c r="C595" s="3"/>
     </row>
     <row r="596" ht="15.75" customHeight="1">
-      <c r="C596" s="2"/>
+      <c r="C596" s="3"/>
     </row>
     <row r="597" ht="15.75" customHeight="1">
-      <c r="C597" s="2"/>
+      <c r="C597" s="3"/>
     </row>
     <row r="598" ht="15.75" customHeight="1">
-      <c r="C598" s="2"/>
+      <c r="C598" s="3"/>
     </row>
     <row r="599" ht="15.75" customHeight="1">
-      <c r="C599" s="2"/>
+      <c r="C599" s="3"/>
     </row>
     <row r="600" ht="15.75" customHeight="1">
-      <c r="C600" s="2"/>
+      <c r="C600" s="3"/>
     </row>
     <row r="601" ht="15.75" customHeight="1">
-      <c r="C601" s="2"/>
+      <c r="C601" s="3"/>
     </row>
     <row r="602" ht="15.75" customHeight="1">
-      <c r="C602" s="2"/>
+      <c r="C602" s="3"/>
     </row>
     <row r="603" ht="15.75" customHeight="1">
-      <c r="C603" s="2"/>
+      <c r="C603" s="3"/>
     </row>
     <row r="604" ht="15.75" customHeight="1">
-      <c r="C604" s="2"/>
+      <c r="C604" s="3"/>
     </row>
     <row r="605" ht="15.75" customHeight="1">
-      <c r="C605" s="2"/>
+      <c r="C605" s="3"/>
     </row>
     <row r="606" ht="15.75" customHeight="1">
-      <c r="C606" s="2"/>
+      <c r="C606" s="3"/>
     </row>
     <row r="607" ht="15.75" customHeight="1">
-      <c r="C607" s="2"/>
+      <c r="C607" s="3"/>
     </row>
     <row r="608" ht="15.75" customHeight="1">
-      <c r="C608" s="2"/>
+      <c r="C608" s="3"/>
     </row>
     <row r="609" ht="15.75" customHeight="1">
-      <c r="C609" s="2"/>
+      <c r="C609" s="3"/>
     </row>
     <row r="610" ht="15.75" customHeight="1">
-      <c r="C610" s="2"/>
+      <c r="C610" s="3"/>
     </row>
     <row r="611" ht="15.75" customHeight="1">
-      <c r="C611" s="2"/>
+      <c r="C611" s="3"/>
     </row>
     <row r="612" ht="15.75" customHeight="1">
-      <c r="C612" s="2"/>
+      <c r="C612" s="3"/>
     </row>
     <row r="613" ht="15.75" customHeight="1">
-      <c r="C613" s="2"/>
+      <c r="C613" s="3"/>
     </row>
     <row r="614" ht="15.75" customHeight="1">
-      <c r="C614" s="2"/>
+      <c r="C614" s="3"/>
     </row>
     <row r="615" ht="15.75" customHeight="1">
-      <c r="C615" s="2"/>
+      <c r="C615" s="3"/>
     </row>
     <row r="616" ht="15.75" customHeight="1">
-      <c r="C616" s="2"/>
+      <c r="C616" s="3"/>
     </row>
     <row r="617" ht="15.75" customHeight="1">
-      <c r="C617" s="2"/>
+      <c r="C617" s="3"/>
     </row>
     <row r="618" ht="15.75" customHeight="1">
-      <c r="C618" s="2"/>
+      <c r="C618" s="3"/>
     </row>
     <row r="619" ht="15.75" customHeight="1">
-      <c r="C619" s="2"/>
+      <c r="C619" s="3"/>
     </row>
     <row r="620" ht="15.75" customHeight="1">
-      <c r="C620" s="2"/>
+      <c r="C620" s="3"/>
     </row>
     <row r="621" ht="15.75" customHeight="1">
-      <c r="C621" s="2"/>
+      <c r="C621" s="3"/>
     </row>
     <row r="622" ht="15.75" customHeight="1">
-      <c r="C622" s="2"/>
+      <c r="C622" s="3"/>
     </row>
     <row r="623" ht="15.75" customHeight="1">
-      <c r="C623" s="2"/>
+      <c r="C623" s="3"/>
     </row>
     <row r="624" ht="15.75" customHeight="1">
-      <c r="C624" s="2"/>
+      <c r="C624" s="3"/>
     </row>
     <row r="625" ht="15.75" customHeight="1">
-      <c r="C625" s="2"/>
+      <c r="C625" s="3"/>
     </row>
     <row r="626" ht="15.75" customHeight="1">
-      <c r="C626" s="2"/>
+      <c r="C626" s="3"/>
     </row>
     <row r="627" ht="15.75" customHeight="1">
-      <c r="C627" s="2"/>
+      <c r="C627" s="3"/>
     </row>
     <row r="628" ht="15.75" customHeight="1">
-      <c r="C628" s="2"/>
+      <c r="C628" s="3"/>
     </row>
     <row r="629" ht="15.75" customHeight="1">
-      <c r="C629" s="2"/>
+      <c r="C629" s="3"/>
     </row>
     <row r="630" ht="15.75" customHeight="1">
-      <c r="C630" s="2"/>
+      <c r="C630" s="3"/>
     </row>
     <row r="631" ht="15.75" customHeight="1">
-      <c r="C631" s="2"/>
+      <c r="C631" s="3"/>
     </row>
     <row r="632" ht="15.75" customHeight="1">
-      <c r="C632" s="2"/>
+      <c r="C632" s="3"/>
     </row>
     <row r="633" ht="15.75" customHeight="1">
-      <c r="C633" s="2"/>
+      <c r="C633" s="3"/>
     </row>
     <row r="634" ht="15.75" customHeight="1">
-      <c r="C634" s="2"/>
+      <c r="C634" s="3"/>
     </row>
     <row r="635" ht="15.75" customHeight="1">
-      <c r="C635" s="2"/>
+      <c r="C635" s="3"/>
     </row>
     <row r="636" ht="15.75" customHeight="1">
-      <c r="C636" s="2"/>
+      <c r="C636" s="3"/>
     </row>
     <row r="637" ht="15.75" customHeight="1">
-      <c r="C637" s="2"/>
+      <c r="C637" s="3"/>
     </row>
     <row r="638" ht="15.75" customHeight="1">
-      <c r="C638" s="2"/>
+      <c r="C638" s="3"/>
     </row>
     <row r="639" ht="15.75" customHeight="1">
-      <c r="C639" s="2"/>
+      <c r="C639" s="3"/>
     </row>
     <row r="640" ht="15.75" customHeight="1">
-      <c r="C640" s="2"/>
+      <c r="C640" s="3"/>
     </row>
     <row r="641" ht="15.75" customHeight="1">
-      <c r="C641" s="2"/>
+      <c r="C641" s="3"/>
     </row>
     <row r="642" ht="15.75" customHeight="1">
-      <c r="C642" s="2"/>
+      <c r="C642" s="3"/>
     </row>
     <row r="643" ht="15.75" customHeight="1">
-      <c r="C643" s="2"/>
+      <c r="C643" s="3"/>
     </row>
     <row r="644" ht="15.75" customHeight="1">
-      <c r="C644" s="2"/>
+      <c r="C644" s="3"/>
     </row>
     <row r="645" ht="15.75" customHeight="1">
-      <c r="C645" s="2"/>
+      <c r="C645" s="3"/>
     </row>
     <row r="646" ht="15.75" customHeight="1">
-      <c r="C646" s="2"/>
+      <c r="C646" s="3"/>
     </row>
     <row r="647" ht="15.75" customHeight="1">
-      <c r="C647" s="2"/>
+      <c r="C647" s="3"/>
     </row>
     <row r="648" ht="15.75" customHeight="1">
-      <c r="C648" s="2"/>
+      <c r="C648" s="3"/>
     </row>
     <row r="649" ht="15.75" customHeight="1">
-      <c r="C649" s="2"/>
+      <c r="C649" s="3"/>
     </row>
     <row r="650" ht="15.75" customHeight="1">
-      <c r="C650" s="2"/>
+      <c r="C650" s="3"/>
     </row>
     <row r="651" ht="15.75" customHeight="1">
-      <c r="C651" s="2"/>
+      <c r="C651" s="3"/>
     </row>
     <row r="652" ht="15.75" customHeight="1">
-      <c r="C652" s="2"/>
+      <c r="C652" s="3"/>
     </row>
     <row r="653" ht="15.75" customHeight="1">
-      <c r="C653" s="2"/>
+      <c r="C653" s="3"/>
     </row>
     <row r="654" ht="15.75" customHeight="1">
-      <c r="C654" s="2"/>
+      <c r="C654" s="3"/>
     </row>
     <row r="655" ht="15.75" customHeight="1">
-      <c r="C655" s="2"/>
+      <c r="C655" s="3"/>
     </row>
     <row r="656" ht="15.75" customHeight="1">
-      <c r="C656" s="2"/>
+      <c r="C656" s="3"/>
     </row>
     <row r="657" ht="15.75" customHeight="1">
-      <c r="C657" s="2"/>
+      <c r="C657" s="3"/>
     </row>
     <row r="658" ht="15.75" customHeight="1">
-      <c r="C658" s="2"/>
+      <c r="C658" s="3"/>
     </row>
     <row r="659" ht="15.75" customHeight="1">
-      <c r="C659" s="2"/>
+      <c r="C659" s="3"/>
     </row>
     <row r="660" ht="15.75" customHeight="1">
-      <c r="C660" s="2"/>
+      <c r="C660" s="3"/>
     </row>
     <row r="661" ht="15.75" customHeight="1">
-      <c r="C661" s="2"/>
+      <c r="C661" s="3"/>
     </row>
     <row r="662" ht="15.75" customHeight="1">
-      <c r="C662" s="2"/>
+      <c r="C662" s="3"/>
     </row>
     <row r="663" ht="15.75" customHeight="1">
-      <c r="C663" s="2"/>
+      <c r="C663" s="3"/>
     </row>
     <row r="664" ht="15.75" customHeight="1">
-      <c r="C664" s="2"/>
+      <c r="C664" s="3"/>
     </row>
     <row r="665" ht="15.75" customHeight="1">
-      <c r="C665" s="2"/>
+      <c r="C665" s="3"/>
     </row>
     <row r="666" ht="15.75" customHeight="1">
-      <c r="C666" s="2"/>
+      <c r="C666" s="3"/>
     </row>
     <row r="667" ht="15.75" customHeight="1">
-      <c r="C667" s="2"/>
+      <c r="C667" s="3"/>
     </row>
     <row r="668" ht="15.75" customHeight="1">
-      <c r="C668" s="2"/>
+      <c r="C668" s="3"/>
     </row>
     <row r="669" ht="15.75" customHeight="1">
-      <c r="C669" s="2"/>
+      <c r="C669" s="3"/>
     </row>
     <row r="670" ht="15.75" customHeight="1">
-      <c r="C670" s="2"/>
+      <c r="C670" s="3"/>
     </row>
     <row r="671" ht="15.75" customHeight="1">
-      <c r="C671" s="2"/>
+      <c r="C671" s="3"/>
     </row>
     <row r="672" ht="15.75" customHeight="1">
-      <c r="C672" s="2"/>
+      <c r="C672" s="3"/>
     </row>
     <row r="673" ht="15.75" customHeight="1">
-      <c r="C673" s="2"/>
+      <c r="C673" s="3"/>
     </row>
     <row r="674" ht="15.75" customHeight="1">
-      <c r="C674" s="2"/>
+      <c r="C674" s="3"/>
     </row>
     <row r="675" ht="15.75" customHeight="1">
-      <c r="C675" s="2"/>
+      <c r="C675" s="3"/>
     </row>
     <row r="676" ht="15.75" customHeight="1">
-      <c r="C676" s="2"/>
+      <c r="C676" s="3"/>
     </row>
     <row r="677" ht="15.75" customHeight="1">
-      <c r="C677" s="2"/>
+      <c r="C677" s="3"/>
     </row>
     <row r="678" ht="15.75" customHeight="1">
-      <c r="C678" s="2"/>
+      <c r="C678" s="3"/>
     </row>
     <row r="679" ht="15.75" customHeight="1">
-      <c r="C679" s="2"/>
+      <c r="C679" s="3"/>
     </row>
     <row r="680" ht="15.75" customHeight="1">
-      <c r="C680" s="2"/>
+      <c r="C680" s="3"/>
     </row>
     <row r="681" ht="15.75" customHeight="1">
-      <c r="C681" s="2"/>
+      <c r="C681" s="3"/>
     </row>
     <row r="682" ht="15.75" customHeight="1">
-      <c r="C682" s="2"/>
+      <c r="C682" s="3"/>
     </row>
     <row r="683" ht="15.75" customHeight="1">
-      <c r="C683" s="2"/>
+      <c r="C683" s="3"/>
     </row>
     <row r="684" ht="15.75" customHeight="1">
-      <c r="C684" s="2"/>
+      <c r="C684" s="3"/>
     </row>
     <row r="685" ht="15.75" customHeight="1">
-      <c r="C685" s="2"/>
+      <c r="C685" s="3"/>
     </row>
     <row r="686" ht="15.75" customHeight="1">
-      <c r="C686" s="2"/>
+      <c r="C686" s="3"/>
     </row>
     <row r="687" ht="15.75" customHeight="1">
-      <c r="C687" s="2"/>
+      <c r="C687" s="3"/>
     </row>
     <row r="688" ht="15.75" customHeight="1">
-      <c r="C688" s="2"/>
+      <c r="C688" s="3"/>
     </row>
     <row r="689" ht="15.75" customHeight="1">
-      <c r="C689" s="2"/>
+      <c r="C689" s="3"/>
     </row>
     <row r="690" ht="15.75" customHeight="1">
-      <c r="C690" s="2"/>
+      <c r="C690" s="3"/>
     </row>
     <row r="691" ht="15.75" customHeight="1">
-      <c r="C691" s="2"/>
+      <c r="C691" s="3"/>
     </row>
     <row r="692" ht="15.75" customHeight="1">
-      <c r="C692" s="2"/>
+      <c r="C692" s="3"/>
     </row>
     <row r="693" ht="15.75" customHeight="1">
-      <c r="C693" s="2"/>
+      <c r="C693" s="3"/>
     </row>
     <row r="694" ht="15.75" customHeight="1">
-      <c r="C694" s="2"/>
+      <c r="C694" s="3"/>
     </row>
     <row r="695" ht="15.75" customHeight="1">
-      <c r="C695" s="2"/>
+      <c r="C695" s="3"/>
     </row>
     <row r="696" ht="15.75" customHeight="1">
-      <c r="C696" s="2"/>
+      <c r="C696" s="3"/>
     </row>
     <row r="697" ht="15.75" customHeight="1">
-      <c r="C697" s="2"/>
+      <c r="C697" s="3"/>
     </row>
     <row r="698" ht="15.75" customHeight="1">
-      <c r="C698" s="2"/>
+      <c r="C698" s="3"/>
     </row>
     <row r="699" ht="15.75" customHeight="1">
-      <c r="C699" s="2"/>
+      <c r="C699" s="3"/>
     </row>
     <row r="700" ht="15.75" customHeight="1">
-      <c r="C700" s="2"/>
+      <c r="C700" s="3"/>
     </row>
     <row r="701" ht="15.75" customHeight="1">
-      <c r="C701" s="2"/>
+      <c r="C701" s="3"/>
     </row>
     <row r="702" ht="15.75" customHeight="1">
-      <c r="C702" s="2"/>
+      <c r="C702" s="3"/>
     </row>
     <row r="703" ht="15.75" customHeight="1">
-      <c r="C703" s="2"/>
+      <c r="C703" s="3"/>
     </row>
     <row r="704" ht="15.75" customHeight="1">
-      <c r="C704" s="2"/>
+      <c r="C704" s="3"/>
     </row>
     <row r="705" ht="15.75" customHeight="1">
-      <c r="C705" s="2"/>
+      <c r="C705" s="3"/>
     </row>
     <row r="706" ht="15.75" customHeight="1">
-      <c r="C706" s="2"/>
+      <c r="C706" s="3"/>
     </row>
     <row r="707" ht="15.75" customHeight="1">
-      <c r="C707" s="2"/>
+      <c r="C707" s="3"/>
     </row>
     <row r="708" ht="15.75" customHeight="1">
-      <c r="C708" s="2"/>
+      <c r="C708" s="3"/>
     </row>
     <row r="709" ht="15.75" customHeight="1">
-      <c r="C709" s="2"/>
+      <c r="C709" s="3"/>
     </row>
     <row r="710" ht="15.75" customHeight="1">
-      <c r="C710" s="2"/>
+      <c r="C710" s="3"/>
     </row>
     <row r="711" ht="15.75" customHeight="1">
-      <c r="C711" s="2"/>
+      <c r="C711" s="3"/>
     </row>
     <row r="712" ht="15.75" customHeight="1">
-      <c r="C712" s="2"/>
+      <c r="C712" s="3"/>
     </row>
     <row r="713" ht="15.75" customHeight="1">
-      <c r="C713" s="2"/>
+      <c r="C713" s="3"/>
     </row>
     <row r="714" ht="15.75" customHeight="1">
-      <c r="C714" s="2"/>
+      <c r="C714" s="3"/>
     </row>
     <row r="715" ht="15.75" customHeight="1">
-      <c r="C715" s="2"/>
+      <c r="C715" s="3"/>
     </row>
     <row r="716" ht="15.75" customHeight="1">
-      <c r="C716" s="2"/>
+      <c r="C716" s="3"/>
     </row>
     <row r="717" ht="15.75" customHeight="1">
-      <c r="C717" s="2"/>
+      <c r="C717" s="3"/>
     </row>
     <row r="718" ht="15.75" customHeight="1">
-      <c r="C718" s="2"/>
+      <c r="C718" s="3"/>
     </row>
     <row r="719" ht="15.75" customHeight="1">
-      <c r="C719" s="2"/>
+      <c r="C719" s="3"/>
     </row>
     <row r="720" ht="15.75" customHeight="1">
-      <c r="C720" s="2"/>
+      <c r="C720" s="3"/>
     </row>
     <row r="721" ht="15.75" customHeight="1">
-      <c r="C721" s="2"/>
+      <c r="C721" s="3"/>
     </row>
     <row r="722" ht="15.75" customHeight="1">
-      <c r="C722" s="2"/>
+      <c r="C722" s="3"/>
     </row>
     <row r="723" ht="15.75" customHeight="1">
-      <c r="C723" s="2"/>
+      <c r="C723" s="3"/>
     </row>
     <row r="724" ht="15.75" customHeight="1">
-      <c r="C724" s="2"/>
+      <c r="C724" s="3"/>
     </row>
     <row r="725" ht="15.75" customHeight="1">
-      <c r="C725" s="2"/>
+      <c r="C725" s="3"/>
     </row>
     <row r="726" ht="15.75" customHeight="1">
-      <c r="C726" s="2"/>
+      <c r="C726" s="3"/>
     </row>
     <row r="727" ht="15.75" customHeight="1">
-      <c r="C727" s="2"/>
+      <c r="C727" s="3"/>
     </row>
     <row r="728" ht="15.75" customHeight="1">
-      <c r="C728" s="2"/>
+      <c r="C728" s="3"/>
     </row>
     <row r="729" ht="15.75" customHeight="1">
-      <c r="C729" s="2"/>
+      <c r="C729" s="3"/>
     </row>
     <row r="730" ht="15.75" customHeight="1">
-      <c r="C730" s="2"/>
+      <c r="C730" s="3"/>
     </row>
     <row r="731" ht="15.75" customHeight="1">
-      <c r="C731" s="2"/>
+      <c r="C731" s="3"/>
     </row>
     <row r="732" ht="15.75" customHeight="1">
-      <c r="C732" s="2"/>
+      <c r="C732" s="3"/>
     </row>
     <row r="733" ht="15.75" customHeight="1">
-      <c r="C733" s="2"/>
+      <c r="C733" s="3"/>
     </row>
     <row r="734" ht="15.75" customHeight="1">
-      <c r="C734" s="2"/>
+      <c r="C734" s="3"/>
     </row>
     <row r="735" ht="15.75" customHeight="1">
-      <c r="C735" s="2"/>
+      <c r="C735" s="3"/>
     </row>
     <row r="736" ht="15.75" customHeight="1">
-      <c r="C736" s="2"/>
+      <c r="C736" s="3"/>
     </row>
     <row r="737" ht="15.75" customHeight="1">
-      <c r="C737" s="2"/>
+      <c r="C737" s="3"/>
     </row>
     <row r="738" ht="15.75" customHeight="1">
-      <c r="C738" s="2"/>
+      <c r="C738" s="3"/>
     </row>
     <row r="739" ht="15.75" customHeight="1">
-      <c r="C739" s="2"/>
+      <c r="C739" s="3"/>
     </row>
     <row r="740" ht="15.75" customHeight="1">
-      <c r="C740" s="2"/>
+      <c r="C740" s="3"/>
     </row>
     <row r="741" ht="15.75" customHeight="1">
-      <c r="C741" s="2"/>
+      <c r="C741" s="3"/>
     </row>
     <row r="742" ht="15.75" customHeight="1">
-      <c r="C742" s="2"/>
+      <c r="C742" s="3"/>
     </row>
     <row r="743" ht="15.75" customHeight="1">
-      <c r="C743" s="2"/>
+      <c r="C743" s="3"/>
     </row>
     <row r="744" ht="15.75" customHeight="1">
-      <c r="C744" s="2"/>
+      <c r="C744" s="3"/>
     </row>
     <row r="745" ht="15.75" customHeight="1">
-      <c r="C745" s="2"/>
+      <c r="C745" s="3"/>
     </row>
     <row r="746" ht="15.75" customHeight="1">
-      <c r="C746" s="2"/>
+      <c r="C746" s="3"/>
     </row>
     <row r="747" ht="15.75" customHeight="1">
-      <c r="C747" s="2"/>
+      <c r="C747" s="3"/>
     </row>
     <row r="748" ht="15.75" customHeight="1">
-      <c r="C748" s="2"/>
+      <c r="C748" s="3"/>
     </row>
     <row r="749" ht="15.75" customHeight="1">
-      <c r="C749" s="2"/>
+      <c r="C749" s="3"/>
     </row>
     <row r="750" ht="15.75" customHeight="1">
-      <c r="C750" s="2"/>
+      <c r="C750" s="3"/>
     </row>
     <row r="751" ht="15.75" customHeight="1">
-      <c r="C751" s="2"/>
+      <c r="C751" s="3"/>
     </row>
     <row r="752" ht="15.75" customHeight="1">
-      <c r="C752" s="2"/>
+      <c r="C752" s="3"/>
     </row>
     <row r="753" ht="15.75" customHeight="1">
-      <c r="C753" s="2"/>
+      <c r="C753" s="3"/>
     </row>
     <row r="754" ht="15.75" customHeight="1">
-      <c r="C754" s="2"/>
+      <c r="C754" s="3"/>
     </row>
     <row r="755" ht="15.75" customHeight="1">
-      <c r="C755" s="2"/>
+      <c r="C755" s="3"/>
     </row>
     <row r="756" ht="15.75" customHeight="1">
-      <c r="C756" s="2"/>
+      <c r="C756" s="3"/>
     </row>
     <row r="757" ht="15.75" customHeight="1">
-      <c r="C757" s="2"/>
+      <c r="C757" s="3"/>
     </row>
     <row r="758" ht="15.75" customHeight="1">
-      <c r="C758" s="2"/>
+      <c r="C758" s="3"/>
     </row>
     <row r="759" ht="15.75" customHeight="1">
-      <c r="C759" s="2"/>
+      <c r="C759" s="3"/>
     </row>
     <row r="760" ht="15.75" customHeight="1">
-      <c r="C760" s="2"/>
+      <c r="C760" s="3"/>
     </row>
     <row r="761" ht="15.75" customHeight="1">
-      <c r="C761" s="2"/>
+      <c r="C761" s="3"/>
     </row>
     <row r="762" ht="15.75" customHeight="1">
-      <c r="C762" s="2"/>
+      <c r="C762" s="3"/>
     </row>
     <row r="763" ht="15.75" customHeight="1">
-      <c r="C763" s="2"/>
+      <c r="C763" s="3"/>
     </row>
     <row r="764" ht="15.75" customHeight="1">
-      <c r="C764" s="2"/>
+      <c r="C764" s="3"/>
     </row>
     <row r="765" ht="15.75" customHeight="1">
-      <c r="C765" s="2"/>
+      <c r="C765" s="3"/>
     </row>
     <row r="766" ht="15.75" customHeight="1">
-      <c r="C766" s="2"/>
+      <c r="C766" s="3"/>
     </row>
     <row r="767" ht="15.75" customHeight="1">
-      <c r="C767" s="2"/>
+      <c r="C767" s="3"/>
     </row>
     <row r="768" ht="15.75" customHeight="1">
-      <c r="C768" s="2"/>
+      <c r="C768" s="3"/>
     </row>
     <row r="769" ht="15.75" customHeight="1">
-      <c r="C769" s="2"/>
+      <c r="C769" s="3"/>
     </row>
     <row r="770" ht="15.75" customHeight="1">
-      <c r="C770" s="2"/>
+      <c r="C770" s="3"/>
     </row>
     <row r="771" ht="15.75" customHeight="1">
-      <c r="C771" s="2"/>
+      <c r="C771" s="3"/>
     </row>
     <row r="772" ht="15.75" customHeight="1">
-      <c r="C772" s="2"/>
+      <c r="C772" s="3"/>
     </row>
     <row r="773" ht="15.75" customHeight="1">
-      <c r="C773" s="2"/>
+      <c r="C773" s="3"/>
     </row>
     <row r="774" ht="15.75" customHeight="1">
-      <c r="C774" s="2"/>
+      <c r="C774" s="3"/>
     </row>
     <row r="775" ht="15.75" customHeight="1">
-      <c r="C775" s="2"/>
+      <c r="C775" s="3"/>
     </row>
     <row r="776" ht="15.75" customHeight="1">
-      <c r="C776" s="2"/>
+      <c r="C776" s="3"/>
     </row>
     <row r="777" ht="15.75" customHeight="1">
-      <c r="C777" s="2"/>
+      <c r="C777" s="3"/>
     </row>
     <row r="778" ht="15.75" customHeight="1">
-      <c r="C778" s="2"/>
+      <c r="C778" s="3"/>
     </row>
     <row r="779" ht="15.75" customHeight="1">
-      <c r="C779" s="2"/>
+      <c r="C779" s="3"/>
     </row>
     <row r="780" ht="15.75" customHeight="1">
-      <c r="C780" s="2"/>
+      <c r="C780" s="3"/>
     </row>
     <row r="781" ht="15.75" customHeight="1">
-      <c r="C781" s="2"/>
+      <c r="C781" s="3"/>
     </row>
     <row r="782" ht="15.75" customHeight="1">
-      <c r="C782" s="2"/>
+      <c r="C782" s="3"/>
     </row>
     <row r="783" ht="15.75" customHeight="1">
-      <c r="C783" s="2"/>
+      <c r="C783" s="3"/>
     </row>
     <row r="784" ht="15.75" customHeight="1">
-      <c r="C784" s="2"/>
+      <c r="C784" s="3"/>
     </row>
     <row r="785" ht="15.75" customHeight="1">
-      <c r="C785" s="2"/>
+      <c r="C785" s="3"/>
     </row>
     <row r="786" ht="15.75" customHeight="1">
-      <c r="C786" s="2"/>
+      <c r="C786" s="3"/>
     </row>
     <row r="787" ht="15.75" customHeight="1">
-      <c r="C787" s="2"/>
+      <c r="C787" s="3"/>
     </row>
     <row r="788" ht="15.75" customHeight="1">
-      <c r="C788" s="2"/>
+      <c r="C788" s="3"/>
     </row>
     <row r="789" ht="15.75" customHeight="1">
-      <c r="C789" s="2"/>
+      <c r="C789" s="3"/>
     </row>
     <row r="790" ht="15.75" customHeight="1">
-      <c r="C790" s="2"/>
+      <c r="C790" s="3"/>
     </row>
     <row r="791" ht="15.75" customHeight="1">
-      <c r="C791" s="2"/>
+      <c r="C791" s="3"/>
     </row>
     <row r="792" ht="15.75" customHeight="1">
-      <c r="C792" s="2"/>
+      <c r="C792" s="3"/>
     </row>
     <row r="793" ht="15.75" customHeight="1">
-      <c r="C793" s="2"/>
+      <c r="C793" s="3"/>
     </row>
     <row r="794" ht="15.75" customHeight="1">
-      <c r="C794" s="2"/>
+      <c r="C794" s="3"/>
     </row>
     <row r="795" ht="15.75" customHeight="1">
-      <c r="C795" s="2"/>
+      <c r="C795" s="3"/>
     </row>
     <row r="796" ht="15.75" customHeight="1">
-      <c r="C796" s="2"/>
+      <c r="C796" s="3"/>
     </row>
     <row r="797" ht="15.75" customHeight="1">
-      <c r="C797" s="2"/>
+      <c r="C797" s="3"/>
     </row>
     <row r="798" ht="15.75" customHeight="1">
-      <c r="C798" s="2"/>
+      <c r="C798" s="3"/>
     </row>
     <row r="799" ht="15.75" customHeight="1">
-      <c r="C799" s="2"/>
+      <c r="C799" s="3"/>
     </row>
     <row r="800" ht="15.75" customHeight="1">
-      <c r="C800" s="2"/>
+      <c r="C800" s="3"/>
     </row>
     <row r="801" ht="15.75" customHeight="1">
-      <c r="C801" s="2"/>
+      <c r="C801" s="3"/>
     </row>
     <row r="802" ht="15.75" customHeight="1">
-      <c r="C802" s="2"/>
+      <c r="C802" s="3"/>
     </row>
     <row r="803" ht="15.75" customHeight="1">
-      <c r="C803" s="2"/>
+      <c r="C803" s="3"/>
     </row>
     <row r="804" ht="15.75" customHeight="1">
-      <c r="C804" s="2"/>
+      <c r="C804" s="3"/>
     </row>
     <row r="805" ht="15.75" customHeight="1">
-      <c r="C805" s="2"/>
+      <c r="C805" s="3"/>
     </row>
     <row r="806" ht="15.75" customHeight="1">
-      <c r="C806" s="2"/>
+      <c r="C806" s="3"/>
     </row>
     <row r="807" ht="15.75" customHeight="1">
-      <c r="C807" s="2"/>
+      <c r="C807" s="3"/>
     </row>
     <row r="808" ht="15.75" customHeight="1">
-      <c r="C808" s="2"/>
+      <c r="C808" s="3"/>
     </row>
     <row r="809" ht="15.75" customHeight="1">
-      <c r="C809" s="2"/>
+      <c r="C809" s="3"/>
     </row>
     <row r="810" ht="15.75" customHeight="1">
-      <c r="C810" s="2"/>
+      <c r="C810" s="3"/>
     </row>
     <row r="811" ht="15.75" customHeight="1">
-      <c r="C811" s="2"/>
+      <c r="C811" s="3"/>
     </row>
     <row r="812" ht="15.75" customHeight="1">
-      <c r="C812" s="2"/>
+      <c r="C812" s="3"/>
     </row>
     <row r="813" ht="15.75" customHeight="1">
-      <c r="C813" s="2"/>
+      <c r="C813" s="3"/>
     </row>
     <row r="814" ht="15.75" customHeight="1">
-      <c r="C814" s="2"/>
+      <c r="C814" s="3"/>
     </row>
     <row r="815" ht="15.75" customHeight="1">
-      <c r="C815" s="2"/>
+      <c r="C815" s="3"/>
     </row>
     <row r="816" ht="15.75" customHeight="1">
-      <c r="C816" s="2"/>
+      <c r="C816" s="3"/>
     </row>
     <row r="817" ht="15.75" customHeight="1">
-      <c r="C817" s="2"/>
+      <c r="C817" s="3"/>
     </row>
     <row r="818" ht="15.75" customHeight="1">
-      <c r="C818" s="2"/>
+      <c r="C818" s="3"/>
     </row>
     <row r="819" ht="15.75" customHeight="1">
-      <c r="C819" s="2"/>
+      <c r="C819" s="3"/>
     </row>
     <row r="820" ht="15.75" customHeight="1">
-      <c r="C820" s="2"/>
+      <c r="C820" s="3"/>
     </row>
     <row r="821" ht="15.75" customHeight="1">
-      <c r="C821" s="2"/>
+      <c r="C821" s="3"/>
     </row>
     <row r="822" ht="15.75" customHeight="1">
-      <c r="C822" s="2"/>
+      <c r="C822" s="3"/>
     </row>
     <row r="823" ht="15.75" customHeight="1">
-      <c r="C823" s="2"/>
+      <c r="C823" s="3"/>
     </row>
     <row r="824" ht="15.75" customHeight="1">
-      <c r="C824" s="2"/>
+      <c r="C824" s="3"/>
     </row>
     <row r="825" ht="15.75" customHeight="1">
-      <c r="C825" s="2"/>
+      <c r="C825" s="3"/>
     </row>
     <row r="826" ht="15.75" customHeight="1">
-      <c r="C826" s="2"/>
+      <c r="C826" s="3"/>
     </row>
     <row r="827" ht="15.75" customHeight="1">
-      <c r="C827" s="2"/>
+      <c r="C827" s="3"/>
     </row>
     <row r="828" ht="15.75" customHeight="1">
-      <c r="C828" s="2"/>
+      <c r="C828" s="3"/>
     </row>
     <row r="829" ht="15.75" customHeight="1">
-      <c r="C829" s="2"/>
+      <c r="C829" s="3"/>
     </row>
     <row r="830" ht="15.75" customHeight="1">
-      <c r="C830" s="2"/>
+      <c r="C830" s="3"/>
     </row>
     <row r="831" ht="15.75" customHeight="1">
-      <c r="C831" s="2"/>
+      <c r="C831" s="3"/>
     </row>
     <row r="832" ht="15.75" customHeight="1">
-      <c r="C832" s="2"/>
+      <c r="C832" s="3"/>
     </row>
     <row r="833" ht="15.75" customHeight="1">
-      <c r="C833" s="2"/>
+      <c r="C833" s="3"/>
     </row>
     <row r="834" ht="15.75" customHeight="1">
-      <c r="C834" s="2"/>
+      <c r="C834" s="3"/>
     </row>
     <row r="835" ht="15.75" customHeight="1">
-      <c r="C835" s="2"/>
+      <c r="C835" s="3"/>
     </row>
     <row r="836" ht="15.75" customHeight="1">
-      <c r="C836" s="2"/>
+      <c r="C836" s="3"/>
     </row>
     <row r="837" ht="15.75" customHeight="1">
-      <c r="C837" s="2"/>
+      <c r="C837" s="3"/>
     </row>
     <row r="838" ht="15.75" customHeight="1">
-      <c r="C838" s="2"/>
+      <c r="C838" s="3"/>
     </row>
     <row r="839" ht="15.75" customHeight="1">
-      <c r="C839" s="2"/>
+      <c r="C839" s="3"/>
     </row>
     <row r="840" ht="15.75" customHeight="1">
-      <c r="C840" s="2"/>
+      <c r="C840" s="3"/>
     </row>
     <row r="841" ht="15.75" customHeight="1">
-      <c r="C841" s="2"/>
+      <c r="C841" s="3"/>
     </row>
     <row r="842" ht="15.75" customHeight="1">
-      <c r="C842" s="2"/>
+      <c r="C842" s="3"/>
     </row>
     <row r="843" ht="15.75" customHeight="1">
-      <c r="C843" s="2"/>
+      <c r="C843" s="3"/>
     </row>
     <row r="844" ht="15.75" customHeight="1">
-      <c r="C844" s="2"/>
+      <c r="C844" s="3"/>
     </row>
     <row r="845" ht="15.75" customHeight="1">
-      <c r="C845" s="2"/>
+      <c r="C845" s="3"/>
     </row>
     <row r="846" ht="15.75" customHeight="1">
-      <c r="C846" s="2"/>
+      <c r="C846" s="3"/>
     </row>
     <row r="847" ht="15.75" customHeight="1">
-      <c r="C847" s="2"/>
+      <c r="C847" s="3"/>
     </row>
     <row r="848" ht="15.75" customHeight="1">
-      <c r="C848" s="2"/>
+      <c r="C848" s="3"/>
     </row>
     <row r="849" ht="15.75" customHeight="1">
-      <c r="C849" s="2"/>
+      <c r="C849" s="3"/>
     </row>
     <row r="850" ht="15.75" customHeight="1">
-      <c r="C850" s="2"/>
+      <c r="C850" s="3"/>
     </row>
     <row r="851" ht="15.75" customHeight="1">
-      <c r="C851" s="2"/>
+      <c r="C851" s="3"/>
     </row>
     <row r="852" ht="15.75" customHeight="1">
-      <c r="C852" s="2"/>
+      <c r="C852" s="3"/>
     </row>
     <row r="853" ht="15.75" customHeight="1">
-      <c r="C853" s="2"/>
+      <c r="C853" s="3"/>
     </row>
     <row r="854" ht="15.75" customHeight="1">
-      <c r="C854" s="2"/>
+      <c r="C854" s="3"/>
     </row>
     <row r="855" ht="15.75" customHeight="1">
-      <c r="C855" s="2"/>
+      <c r="C855" s="3"/>
     </row>
     <row r="856" ht="15.75" customHeight="1">
-      <c r="C856" s="2"/>
+      <c r="C856" s="3"/>
     </row>
     <row r="857" ht="15.75" customHeight="1">
-      <c r="C857" s="2"/>
+      <c r="C857" s="3"/>
     </row>
     <row r="858" ht="15.75" customHeight="1">
-      <c r="C858" s="2"/>
+      <c r="C858" s="3"/>
     </row>
     <row r="859" ht="15.75" customHeight="1">
-      <c r="C859" s="2"/>
+      <c r="C859" s="3"/>
     </row>
     <row r="860" ht="15.75" customHeight="1">
-      <c r="C860" s="2"/>
+      <c r="C860" s="3"/>
     </row>
     <row r="861" ht="15.75" customHeight="1">
-      <c r="C861" s="2"/>
+      <c r="C861" s="3"/>
     </row>
     <row r="862" ht="15.75" customHeight="1">
-      <c r="C862" s="2"/>
+      <c r="C862" s="3"/>
     </row>
     <row r="863" ht="15.75" customHeight="1">
-      <c r="C863" s="2"/>
+      <c r="C863" s="3"/>
     </row>
     <row r="864" ht="15.75" customHeight="1">
-      <c r="C864" s="2"/>
+      <c r="C864" s="3"/>
     </row>
     <row r="865" ht="15.75" customHeight="1">
-      <c r="C865" s="2"/>
+      <c r="C865" s="3"/>
     </row>
     <row r="866" ht="15.75" customHeight="1">
-      <c r="C866" s="2"/>
+      <c r="C866" s="3"/>
     </row>
     <row r="867" ht="15.75" customHeight="1">
-      <c r="C867" s="2"/>
+      <c r="C867" s="3"/>
     </row>
     <row r="868" ht="15.75" customHeight="1">
-      <c r="C868" s="2"/>
+      <c r="C868" s="3"/>
     </row>
     <row r="869" ht="15.75" customHeight="1">
-      <c r="C869" s="2"/>
+      <c r="C869" s="3"/>
     </row>
     <row r="870" ht="15.75" customHeight="1">
-      <c r="C870" s="2"/>
+      <c r="C870" s="3"/>
     </row>
     <row r="871" ht="15.75" customHeight="1">
-      <c r="C871" s="2"/>
+      <c r="C871" s="3"/>
     </row>
     <row r="872" ht="15.75" customHeight="1">
-      <c r="C872" s="2"/>
+      <c r="C872" s="3"/>
     </row>
     <row r="873" ht="15.75" customHeight="1">
-      <c r="C873" s="2"/>
+      <c r="C873" s="3"/>
     </row>
     <row r="874" ht="15.75" customHeight="1">
-      <c r="C874" s="2"/>
+      <c r="C874" s="3"/>
     </row>
     <row r="875" ht="15.75" customHeight="1">
-      <c r="C875" s="2"/>
+      <c r="C875" s="3"/>
     </row>
     <row r="876" ht="15.75" customHeight="1">
-      <c r="C876" s="2"/>
+      <c r="C876" s="3"/>
     </row>
     <row r="877" ht="15.75" customHeight="1">
-      <c r="C877" s="2"/>
+      <c r="C877" s="3"/>
     </row>
     <row r="878" ht="15.75" customHeight="1">
-      <c r="C878" s="2"/>
+      <c r="C878" s="3"/>
     </row>
     <row r="879" ht="15.75" customHeight="1">
-      <c r="C879" s="2"/>
+      <c r="C879" s="3"/>
     </row>
     <row r="880" ht="15.75" customHeight="1">
-      <c r="C880" s="2"/>
+      <c r="C880" s="3"/>
     </row>
     <row r="881" ht="15.75" customHeight="1">
-      <c r="C881" s="2"/>
+      <c r="C881" s="3"/>
     </row>
     <row r="882" ht="15.75" customHeight="1">
-      <c r="C882" s="2"/>
+      <c r="C882" s="3"/>
     </row>
     <row r="883" ht="15.75" customHeight="1">
-      <c r="C883" s="2"/>
+      <c r="C883" s="3"/>
     </row>
     <row r="884" ht="15.75" customHeight="1">
-      <c r="C884" s="2"/>
+      <c r="C884" s="3"/>
     </row>
     <row r="885" ht="15.75" customHeight="1">
-      <c r="C885" s="2"/>
+      <c r="C885" s="3"/>
     </row>
     <row r="886" ht="15.75" customHeight="1">
-      <c r="C886" s="2"/>
+      <c r="C886" s="3"/>
     </row>
     <row r="887" ht="15.75" customHeight="1">
-      <c r="C887" s="2"/>
+      <c r="C887" s="3"/>
     </row>
     <row r="888" ht="15.75" customHeight="1">
-      <c r="C888" s="2"/>
+      <c r="C888" s="3"/>
     </row>
     <row r="889" ht="15.75" customHeight="1">
-      <c r="C889" s="2"/>
+      <c r="C889" s="3"/>
     </row>
     <row r="890" ht="15.75" customHeight="1">
-      <c r="C890" s="2"/>
+      <c r="C890" s="3"/>
     </row>
     <row r="891" ht="15.75" customHeight="1">
-      <c r="C891" s="2"/>
+      <c r="C891" s="3"/>
     </row>
     <row r="892" ht="15.75" customHeight="1">
-      <c r="C892" s="2"/>
+      <c r="C892" s="3"/>
     </row>
     <row r="893" ht="15.75" customHeight="1">
-      <c r="C893" s="2"/>
+      <c r="C893" s="3"/>
     </row>
     <row r="894" ht="15.75" customHeight="1">
-      <c r="C894" s="2"/>
+      <c r="C894" s="3"/>
     </row>
     <row r="895" ht="15.75" customHeight="1">
-      <c r="C895" s="2"/>
+      <c r="C895" s="3"/>
     </row>
     <row r="896" ht="15.75" customHeight="1">
-      <c r="C896" s="2"/>
+      <c r="C896" s="3"/>
     </row>
     <row r="897" ht="15.75" customHeight="1">
-      <c r="C897" s="2"/>
+      <c r="C897" s="3"/>
     </row>
     <row r="898" ht="15.75" customHeight="1">
-      <c r="C898" s="2"/>
+      <c r="C898" s="3"/>
     </row>
     <row r="899" ht="15.75" customHeight="1">
-      <c r="C899" s="2"/>
+      <c r="C899" s="3"/>
     </row>
     <row r="900" ht="15.75" customHeight="1">
-      <c r="C900" s="2"/>
+      <c r="C900" s="3"/>
     </row>
     <row r="901" ht="15.75" customHeight="1">
-      <c r="C901" s="2"/>
+      <c r="C901" s="3"/>
     </row>
     <row r="902" ht="15.75" customHeight="1">
-      <c r="C902" s="2"/>
+      <c r="C902" s="3"/>
     </row>
     <row r="903" ht="15.75" customHeight="1">
-      <c r="C903" s="2"/>
+      <c r="C903" s="3"/>
     </row>
     <row r="904" ht="15.75" customHeight="1">
-      <c r="C904" s="2"/>
+      <c r="C904" s="3"/>
     </row>
     <row r="905" ht="15.75" customHeight="1">
-      <c r="C905" s="2"/>
+      <c r="C905" s="3"/>
     </row>
     <row r="906" ht="15.75" customHeight="1">
-      <c r="C906" s="2"/>
+      <c r="C906" s="3"/>
     </row>
     <row r="907" ht="15.75" customHeight="1">
-      <c r="C907" s="2"/>
+      <c r="C907" s="3"/>
     </row>
     <row r="908" ht="15.75" customHeight="1">
-      <c r="C908" s="2"/>
+      <c r="C908" s="3"/>
     </row>
     <row r="909" ht="15.75" customHeight="1">
-      <c r="C909" s="2"/>
+      <c r="C909" s="3"/>
     </row>
     <row r="910" ht="15.75" customHeight="1">
-      <c r="C910" s="2"/>
+      <c r="C910" s="3"/>
     </row>
     <row r="911" ht="15.75" customHeight="1">
-      <c r="C911" s="2"/>
+      <c r="C911" s="3"/>
     </row>
     <row r="912" ht="15.75" customHeight="1">
-      <c r="C912" s="2"/>
+      <c r="C912" s="3"/>
     </row>
     <row r="913" ht="15.75" customHeight="1">
-      <c r="C913" s="2"/>
+      <c r="C913" s="3"/>
     </row>
     <row r="914" ht="15.75" customHeight="1">
-      <c r="C914" s="2"/>
+      <c r="C914" s="3"/>
     </row>
     <row r="915" ht="15.75" customHeight="1">
-      <c r="C915" s="2"/>
+      <c r="C915" s="3"/>
     </row>
     <row r="916" ht="15.75" customHeight="1">
-      <c r="C916" s="2"/>
+      <c r="C916" s="3"/>
     </row>
     <row r="917" ht="15.75" customHeight="1">
-      <c r="C917" s="2"/>
+      <c r="C917" s="3"/>
     </row>
     <row r="918" ht="15.75" customHeight="1">
-      <c r="C918" s="2"/>
+      <c r="C918" s="3"/>
     </row>
     <row r="919" ht="15.75" customHeight="1">
-      <c r="C919" s="2"/>
+      <c r="C919" s="3"/>
     </row>
     <row r="920" ht="15.75" customHeight="1">
-      <c r="C920" s="2"/>
+      <c r="C920" s="3"/>
     </row>
     <row r="921" ht="15.75" customHeight="1">
-      <c r="C921" s="2"/>
+      <c r="C921" s="3"/>
     </row>
     <row r="922" ht="15.75" customHeight="1">
-      <c r="C922" s="2"/>
+      <c r="C922" s="3"/>
     </row>
     <row r="923" ht="15.75" customHeight="1">
-      <c r="C923" s="2"/>
+      <c r="C923" s="3"/>
     </row>
     <row r="924" ht="15.75" customHeight="1">
-      <c r="C924" s="2"/>
+      <c r="C924" s="3"/>
     </row>
     <row r="925" ht="15.75" customHeight="1">
-      <c r="C925" s="2"/>
+      <c r="C925" s="3"/>
     </row>
     <row r="926" ht="15.75" customHeight="1">
-      <c r="C926" s="2"/>
+      <c r="C926" s="3"/>
     </row>
     <row r="927" ht="15.75" customHeight="1">
-      <c r="C927" s="2"/>
+      <c r="C927" s="3"/>
     </row>
     <row r="928" ht="15.75" customHeight="1">
-      <c r="C928" s="2"/>
+      <c r="C928" s="3"/>
     </row>
     <row r="929" ht="15.75" customHeight="1">
-      <c r="C929" s="2"/>
+      <c r="C929" s="3"/>
     </row>
     <row r="930" ht="15.75" customHeight="1">
-      <c r="C930" s="2"/>
+      <c r="C930" s="3"/>
     </row>
     <row r="931" ht="15.75" customHeight="1">
-      <c r="C931" s="2"/>
+      <c r="C931" s="3"/>
     </row>
     <row r="932" ht="15.75" customHeight="1">
-      <c r="C932" s="2"/>
+      <c r="C932" s="3"/>
     </row>
     <row r="933" ht="15.75" customHeight="1">
-      <c r="C933" s="2"/>
+      <c r="C933" s="3"/>
     </row>
     <row r="934" ht="15.75" customHeight="1">
-      <c r="C934" s="2"/>
+      <c r="C934" s="3"/>
     </row>
     <row r="935" ht="15.75" customHeight="1">
-      <c r="C935" s="2"/>
+      <c r="C935" s="3"/>
     </row>
     <row r="936" ht="15.75" customHeight="1">
-      <c r="C936" s="2"/>
+      <c r="C936" s="3"/>
     </row>
     <row r="937" ht="15.75" customHeight="1">
-      <c r="C937" s="2"/>
+      <c r="C937" s="3"/>
     </row>
     <row r="938" ht="15.75" customHeight="1">
-      <c r="C938" s="2"/>
+      <c r="C938" s="3"/>
     </row>
     <row r="939" ht="15.75" customHeight="1">
-      <c r="C939" s="2"/>
+      <c r="C939" s="3"/>
     </row>
     <row r="940" ht="15.75" customHeight="1">
-      <c r="C940" s="2"/>
+      <c r="C940" s="3"/>
     </row>
     <row r="941" ht="15.75" customHeight="1">
-      <c r="C941" s="2"/>
+      <c r="C941" s="3"/>
     </row>
     <row r="942" ht="15.75" customHeight="1">
-      <c r="C942" s="2"/>
+      <c r="C942" s="3"/>
     </row>
     <row r="943" ht="15.75" customHeight="1">
-      <c r="C943" s="2"/>
+      <c r="C943" s="3"/>
     </row>
     <row r="944" ht="15.75" customHeight="1">
-      <c r="C944" s="2"/>
+      <c r="C944" s="3"/>
     </row>
     <row r="945" ht="15.75" customHeight="1">
-      <c r="C945" s="2"/>
+      <c r="C945" s="3"/>
     </row>
     <row r="946" ht="15.75" customHeight="1">
-      <c r="C946" s="2"/>
+      <c r="C946" s="3"/>
     </row>
     <row r="947" ht="15.75" customHeight="1">
-      <c r="C947" s="2"/>
+      <c r="C947" s="3"/>
     </row>
     <row r="948" ht="15.75" customHeight="1">
-      <c r="C948" s="2"/>
+      <c r="C948" s="3"/>
     </row>
     <row r="949" ht="15.75" customHeight="1">
-      <c r="C949" s="2"/>
+      <c r="C949" s="3"/>
     </row>
     <row r="950" ht="15.75" customHeight="1">
-      <c r="C950" s="2"/>
+      <c r="C950" s="3"/>
     </row>
     <row r="951" ht="15.75" customHeight="1">
-      <c r="C951" s="2"/>
+      <c r="C951" s="3"/>
     </row>
     <row r="952" ht="15.75" customHeight="1">
-      <c r="C952" s="2"/>
+      <c r="C952" s="3"/>
     </row>
     <row r="953" ht="15.75" customHeight="1">
-      <c r="C953" s="2"/>
+      <c r="C953" s="3"/>
     </row>
     <row r="954" ht="15.75" customHeight="1">
-      <c r="C954" s="2"/>
+      <c r="C954" s="3"/>
     </row>
     <row r="955" ht="15.75" customHeight="1">
-      <c r="C955" s="2"/>
+      <c r="C955" s="3"/>
     </row>
     <row r="956" ht="15.75" customHeight="1">
-      <c r="C956" s="2"/>
+      <c r="C956" s="3"/>
     </row>
     <row r="957" ht="15.75" customHeight="1">
-      <c r="C957" s="2"/>
+      <c r="C957" s="3"/>
     </row>
     <row r="958" ht="15.75" customHeight="1">
-      <c r="C958" s="2"/>
+      <c r="C958" s="3"/>
     </row>
     <row r="959" ht="15.75" customHeight="1">
-      <c r="C959" s="2"/>
+      <c r="C959" s="3"/>
     </row>
     <row r="960" ht="15.75" customHeight="1">
-      <c r="C960" s="2"/>
+      <c r="C960" s="3"/>
     </row>
     <row r="961" ht="15.75" customHeight="1">
-      <c r="C961" s="2"/>
+      <c r="C961" s="3"/>
     </row>
     <row r="962" ht="15.75" customHeight="1">
-      <c r="C962" s="2"/>
+      <c r="C962" s="3"/>
     </row>
     <row r="963" ht="15.75" customHeight="1">
-      <c r="C963" s="2"/>
+      <c r="C963" s="3"/>
     </row>
     <row r="964" ht="15.75" customHeight="1">
-      <c r="C964" s="2"/>
+      <c r="C964" s="3"/>
     </row>
     <row r="965" ht="15.75" customHeight="1">
-      <c r="C965" s="2"/>
+      <c r="C965" s="3"/>
     </row>
     <row r="966" ht="15.75" customHeight="1">
-      <c r="C966" s="2"/>
+      <c r="C966" s="3"/>
     </row>
     <row r="967" ht="15.75" customHeight="1">
-      <c r="C967" s="2"/>
+      <c r="C967" s="3"/>
     </row>
     <row r="968" ht="15.75" customHeight="1">
-      <c r="C968" s="2"/>
+      <c r="C968" s="3"/>
     </row>
     <row r="969" ht="15.75" customHeight="1">
-      <c r="C969" s="2"/>
+      <c r="C969" s="3"/>
     </row>
     <row r="970" ht="15.75" customHeight="1">
-      <c r="C970" s="2"/>
+      <c r="C970" s="3"/>
     </row>
     <row r="971" ht="15.75" customHeight="1">
-      <c r="C971" s="2"/>
+      <c r="C971" s="3"/>
     </row>
     <row r="972" ht="15.75" customHeight="1">
-      <c r="C972" s="2"/>
+      <c r="C972" s="3"/>
     </row>
     <row r="973" ht="15.75" customHeight="1">
-      <c r="C973" s="2"/>
+      <c r="C973" s="3"/>
     </row>
     <row r="974" ht="15.75" customHeight="1">
-      <c r="C974" s="2"/>
+      <c r="C974" s="3"/>
     </row>
     <row r="975" ht="15.75" customHeight="1">
-      <c r="C975" s="2"/>
+      <c r="C975" s="3"/>
     </row>
     <row r="976" ht="15.75" customHeight="1">
-      <c r="C976" s="2"/>
+      <c r="C976" s="3"/>
     </row>
     <row r="977" ht="15.75" customHeight="1">
-      <c r="C977" s="2"/>
+      <c r="C977" s="3"/>
     </row>
     <row r="978" ht="15.75" customHeight="1">
-      <c r="C978" s="2"/>
+      <c r="C978" s="3"/>
     </row>
     <row r="979" ht="15.75" customHeight="1">
-      <c r="C979" s="2"/>
+      <c r="C979" s="3"/>
     </row>
     <row r="980" ht="15.75" customHeight="1">
-      <c r="C980" s="2"/>
+      <c r="C980" s="3"/>
     </row>
     <row r="981" ht="15.75" customHeight="1">
-      <c r="C981" s="2"/>
+      <c r="C981" s="3"/>
     </row>
     <row r="982" ht="15.75" customHeight="1">
-      <c r="C982" s="2"/>
+      <c r="C982" s="3"/>
     </row>
     <row r="983" ht="15.75" customHeight="1">
-      <c r="C983" s="2"/>
+      <c r="C983" s="3"/>
     </row>
     <row r="984" ht="15.75" customHeight="1">
-      <c r="C984" s="2"/>
+      <c r="C984" s="3"/>
     </row>
     <row r="985" ht="15.75" customHeight="1">
-      <c r="C985" s="2"/>
+      <c r="C985" s="3"/>
     </row>
     <row r="986" ht="15.75" customHeight="1">
-      <c r="C986" s="2"/>
+      <c r="C986" s="3"/>
     </row>
     <row r="987" ht="15.75" customHeight="1">
-      <c r="C987" s="2"/>
+      <c r="C987" s="3"/>
     </row>
     <row r="988" ht="15.75" customHeight="1">
-      <c r="C988" s="2"/>
+      <c r="C988" s="3"/>
     </row>
     <row r="989" ht="15.75" customHeight="1">
-      <c r="C989" s="2"/>
+      <c r="C989" s="3"/>
     </row>
     <row r="990" ht="15.75" customHeight="1">
-      <c r="C990" s="2"/>
+      <c r="C990" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
